--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8617C696-6E45-48B9-9070-EC7A1C7AF4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C350BF-2D89-421F-AB72-0B3506D17947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="モンスタースキル" sheetId="6" r:id="rId6"/>
     <sheet name="戦績レポート" sheetId="7" r:id="rId7"/>
     <sheet name="各種設定" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
+    <sheet name="crawler" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -6304,8 +6304,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7911971" y="1528349"/>
-          <a:ext cx="1800328" cy="1214718"/>
+          <a:off x="7985930" y="1467837"/>
+          <a:ext cx="1820498" cy="1167653"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -6614,8 +6614,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11175520" y="3059605"/>
-          <a:ext cx="1822530" cy="1963728"/>
+          <a:off x="11283097" y="2938582"/>
+          <a:ext cx="1842700" cy="1889768"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -7166,8 +7166,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4681098" y="1657961"/>
-          <a:ext cx="1869953" cy="3342717"/>
+          <a:off x="4721439" y="1597449"/>
+          <a:ext cx="1890124" cy="3208246"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -7635,8 +7635,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10840271" y="7258650"/>
-          <a:ext cx="2193307" cy="2523422"/>
+          <a:off x="10941124" y="6969538"/>
+          <a:ext cx="2220201" cy="2422569"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -7842,8 +7842,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14334233" y="4816236"/>
-          <a:ext cx="2220036" cy="1720343"/>
+          <a:off x="14468704" y="4627977"/>
+          <a:ext cx="2246929" cy="1653108"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -8272,8 +8272,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6846794" y="5210735"/>
-          <a:ext cx="1781735" cy="1311089"/>
+          <a:off x="6914030" y="5002306"/>
+          <a:ext cx="1795181" cy="1264024"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -8649,8 +8649,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3726679" y="7642890"/>
-          <a:ext cx="2335072" cy="1882107"/>
+          <a:off x="3760297" y="7340331"/>
+          <a:ext cx="2355242" cy="1808149"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -9304,7 +9304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -9318,7 +9318,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -9469,14 +9469,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B3:P98"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="9" style="5" customWidth="1"/>
     <col min="3" max="3" width="18" style="5" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -11820,22 +11820,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -13499,7 +13499,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="40.5">
+    <row r="41" spans="3:17" ht="37.799999999999997">
       <c r="C41" s="47" t="s">
         <v>1057</v>
       </c>
@@ -15251,10 +15251,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -18070,22 +18070,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -34678,7 +34678,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18.75">
+    <row r="510" spans="1:21" ht="18">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -34701,7 +34701,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18.75">
+    <row r="511" spans="1:21" ht="18">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -34724,7 +34724,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18.75">
+    <row r="512" spans="1:21" ht="18">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -34747,7 +34747,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18.75">
+    <row r="513" spans="1:21" ht="18">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -34770,7 +34770,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18.75">
+    <row r="514" spans="1:21" ht="18">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -34793,7 +34793,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18.75">
+    <row r="515" spans="1:21" ht="18">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -34816,7 +34816,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18.75">
+    <row r="516" spans="1:21" ht="18">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -34839,7 +34839,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18.75">
+    <row r="517" spans="1:21" ht="18">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -34862,7 +34862,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18.75">
+    <row r="518" spans="1:21" ht="18">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -34885,7 +34885,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18.75">
+    <row r="519" spans="1:21" ht="18">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -34908,7 +34908,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18.75">
+    <row r="520" spans="1:21" ht="18">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -34931,7 +34931,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18.75">
+    <row r="521" spans="1:21" ht="18">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -34954,7 +34954,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18.75">
+    <row r="522" spans="1:21" ht="18">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -34986,15 +34986,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -35355,13 +35355,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -35462,7 +35462,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C350BF-2D89-421F-AB72-0B3506D17947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90A2938-CF47-4C90-A0DF-D3072D7F35D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="モンスタースキル" sheetId="6" r:id="rId6"/>
     <sheet name="戦績レポート" sheetId="7" r:id="rId7"/>
     <sheet name="各種設定" sheetId="8" r:id="rId8"/>
-    <sheet name="crawler" sheetId="9" r:id="rId9"/>
+    <sheet name="guitarCrawler" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="1468">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5507,6 +5507,928 @@
   </si>
   <si>
     <t>skill043</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ESP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>neck</t>
+  </si>
+  <si>
+    <t>fingerboard</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>nut</t>
+  </si>
+  <si>
+    <t>inlay</t>
+  </si>
+  <si>
+    <t>fret</t>
+  </si>
+  <si>
+    <t>construction</t>
+  </si>
+  <si>
+    <t>tuner</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>pickups</t>
+  </si>
+  <si>
+    <t>controls</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>grip_shape</t>
+  </si>
+  <si>
+    <t>parts_color</t>
+  </si>
+  <si>
+    <t>set_strings</t>
+  </si>
+  <si>
+    <t>body_style</t>
+  </si>
+  <si>
+    <t>body_shape</t>
+  </si>
+  <si>
+    <t>body_material</t>
+  </si>
+  <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>binding</t>
+  </si>
+  <si>
+    <t>body_finish</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t>scale_length</t>
+  </si>
+  <si>
+    <t>fingerboard_material</t>
+  </si>
+  <si>
+    <t>fingerboard_radius</t>
+  </si>
+  <si>
+    <t>fret_count</t>
+  </si>
+  <si>
+    <t>frets</t>
+  </si>
+  <si>
+    <t>nut_material</t>
+  </si>
+  <si>
+    <t>nut_width</t>
+  </si>
+  <si>
+    <t>end_of_board_width</t>
+  </si>
+  <si>
+    <t>inlays</t>
+  </si>
+  <si>
+    <t>joint</t>
+  </si>
+  <si>
+    <t>finish</t>
+  </si>
+  <si>
+    <t>tailpiece</t>
+  </si>
+  <si>
+    <t>tuning_machines</t>
+  </si>
+  <si>
+    <t>pickguard</t>
+  </si>
+  <si>
+    <t>truss_rod</t>
+  </si>
+  <si>
+    <t>truss_rod_cover</t>
+  </si>
+  <si>
+    <t>control_knobs</t>
+  </si>
+  <si>
+    <t>neck_pickup</t>
+  </si>
+  <si>
+    <t>bridge_pickup</t>
+  </si>
+  <si>
+    <t>pickup_selector</t>
+  </si>
+  <si>
+    <t>output_jack</t>
+  </si>
+  <si>
+    <t>strings_gauge</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>accessories</t>
+  </si>
+  <si>
+    <t>switch_tip</t>
+  </si>
+  <si>
+    <t>switch_washer</t>
+  </si>
+  <si>
+    <t>jack_plate_cover</t>
+  </si>
+  <si>
+    <t>strap_buttons</t>
+  </si>
+  <si>
+    <t>Strandberg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>各社スペック属性一覧</t>
+    <rPh sb="0" eb="2">
+      <t>カクシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://strandbergguitars.com/en-US/guitars</t>
+  </si>
+  <si>
+    <t>dexterity</t>
+  </si>
+  <si>
+    <t>neck_construction</t>
+  </si>
+  <si>
+    <t>body_construction</t>
+  </si>
+  <si>
+    <t>scale_configuration</t>
+  </si>
+  <si>
+    <t>neck_profile</t>
+  </si>
+  <si>
+    <t>bridge_type</t>
+  </si>
+  <si>
+    <t>instrument_weight_global</t>
+  </si>
+  <si>
+    <t>instruments_weight_imperial</t>
+  </si>
+  <si>
+    <t>included_instrument_bag_case</t>
+  </si>
+  <si>
+    <t>country_of_manufacturing</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>body_top_material</t>
+  </si>
+  <si>
+    <t>body_finish_color</t>
+  </si>
+  <si>
+    <t>body_finish_type</t>
+  </si>
+  <si>
+    <t>neck_material</t>
+  </si>
+  <si>
+    <t>neck_reinforcement_material</t>
+  </si>
+  <si>
+    <t>fretboard_material</t>
+  </si>
+  <si>
+    <t>fretboard_radius</t>
+  </si>
+  <si>
+    <t>pickup_configuration</t>
+  </si>
+  <si>
+    <t>electronics_type</t>
+  </si>
+  <si>
+    <t>middle_pickup</t>
+  </si>
+  <si>
+    <t>control_set</t>
+  </si>
+  <si>
+    <t>pickup_switching</t>
+  </si>
+  <si>
+    <t>onboard_electronics</t>
+  </si>
+  <si>
+    <t>number_of_frets</t>
+  </si>
+  <si>
+    <t>zero_fret_type</t>
+  </si>
+  <si>
+    <t>main_fret_type</t>
+  </si>
+  <si>
+    <t>neutral_fret</t>
+  </si>
+  <si>
+    <t>nut_width_global</t>
+  </si>
+  <si>
+    <t>nut_width_imperial</t>
+  </si>
+  <si>
+    <t>fretboard_inlays</t>
+  </si>
+  <si>
+    <t>fretboard_side_dots</t>
+  </si>
+  <si>
+    <t>neck_finish_type</t>
+  </si>
+  <si>
+    <t>neck_finish_color</t>
+  </si>
+  <si>
+    <t>hardware_finish</t>
+  </si>
+  <si>
+    <t>string_lock</t>
+  </si>
+  <si>
+    <t>knobs</t>
+  </si>
+  <si>
+    <t>instrument_length_global</t>
+  </si>
+  <si>
+    <t>instrument_length_imperial</t>
+  </si>
+  <si>
+    <t>body_width_global</t>
+  </si>
+  <si>
+    <t>body_width_imperial</t>
+  </si>
+  <si>
+    <t>body_thickness_global</t>
+  </si>
+  <si>
+    <t>body_thickness_imperial</t>
+  </si>
+  <si>
+    <t>neck_thickness_1st_fret_global</t>
+  </si>
+  <si>
+    <t>neck_thickness_1st_fret_imperial</t>
+  </si>
+  <si>
+    <t>neck_thickness_15th_fret_global</t>
+  </si>
+  <si>
+    <t>neck_thickness_15th_fret_imperial</t>
+  </si>
+  <si>
+    <t>string_spacing_at_bridge_global</t>
+  </si>
+  <si>
+    <t>string_spacing_at_bridge_imperial</t>
+  </si>
+  <si>
+    <t>https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB</t>
+  </si>
+  <si>
+    <t>https://espguitars.co.jp/products/esp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クロール開始</t>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Fender</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>fret_size</t>
+  </si>
+  <si>
+    <t>neck_finish</t>
+  </si>
+  <si>
+    <t>position_inlays</t>
+  </si>
+  <si>
+    <t>string_nut</t>
+  </si>
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <t>strings</t>
+  </si>
+  <si>
+    <t>SCHECTER</t>
+  </si>
+  <si>
+    <t>https://schecter.co.jp/guitar/</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>finger_board</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>抽象化後の名称 → 出現回数（多い順）</t>
+  </si>
+  <si>
+    <t>以下は すべての行を抽象化 → カウント → 多い順 に並べた結果。</t>
+  </si>
+  <si>
+    <t>bridge: 6</t>
+  </si>
+  <si>
+    <t>controls: 6</t>
+  </si>
+  <si>
+    <t>inlays: 5</t>
+  </si>
+  <si>
+    <t>pickup: 5</t>
+  </si>
+  <si>
+    <t>fingerboard_material: 4</t>
+  </si>
+  <si>
+    <t>fingerboard_radius: 4</t>
+  </si>
+  <si>
+    <t>neck_finish: 4</t>
+  </si>
+  <si>
+    <t>nut_width: 4</t>
+  </si>
+  <si>
+    <t>scale_length: 4</t>
+  </si>
+  <si>
+    <t>tuning_machines: 3</t>
+  </si>
+  <si>
+    <t>body_finish: 3</t>
+  </si>
+  <si>
+    <t>body_material: 3</t>
+  </si>
+  <si>
+    <t>neck_material: 3</t>
+  </si>
+  <si>
+    <t>frets: 3</t>
+  </si>
+  <si>
+    <t>pickup_config: 3</t>
+  </si>
+  <si>
+    <t>nut: 2</t>
+  </si>
+  <si>
+    <t>color: 2</t>
+  </si>
+  <si>
+    <t>neck: 2</t>
+  </si>
+  <si>
+    <t>body_shape: 2</t>
+  </si>
+  <si>
+    <t>body: 2</t>
+  </si>
+  <si>
+    <t>fingerboard: 2</t>
+  </si>
+  <si>
+    <t>neck_thickness: 2</t>
+  </si>
+  <si>
+    <t>instrument_weight: 2</t>
+  </si>
+  <si>
+    <t>instrument_length: 2</t>
+  </si>
+  <si>
+    <t>body_width: 2</t>
+  </si>
+  <si>
+    <t>body_thickness: 2</t>
+  </si>
+  <si>
+    <t>string_spacing_at_bridge: 2</t>
+  </si>
+  <si>
+    <t>model: 1</t>
+  </si>
+  <si>
+    <t>dexterity: 1</t>
+  </si>
+  <si>
+    <t>body_style: 1</t>
+  </si>
+  <si>
+    <t>neck_construction: 1</t>
+  </si>
+  <si>
+    <t>product_name: 1</t>
+  </si>
+  <si>
+    <t>grip_shape: 1</t>
+  </si>
+  <si>
+    <t>body_construction: 1</t>
+  </si>
+  <si>
+    <t>fret_size: 1</t>
+  </si>
+  <si>
+    <t>top: 1</t>
+  </si>
+  <si>
+    <t>binding: 1</t>
+  </si>
+  <si>
+    <t>neck_profile: 1</t>
+  </si>
+  <si>
+    <t>profile: 1</t>
+  </si>
+  <si>
+    <t>joint: 1</t>
+  </si>
+  <si>
+    <t>pickups: 1</t>
+  </si>
+  <si>
+    <t>included_instrument_bag_case: 1</t>
+  </si>
+  <si>
+    <t>country_of_manufacturing: 1</t>
+  </si>
+  <si>
+    <t>sku: 1</t>
+  </si>
+  <si>
+    <t>position_inlays: 1</t>
+  </si>
+  <si>
+    <t>string_nut: 1</t>
+  </si>
+  <si>
+    <t>parts_color: 1</t>
+  </si>
+  <si>
+    <t>series: 1</t>
+  </si>
+  <si>
+    <t>end_of_board_width: 1</t>
+  </si>
+  <si>
+    <t>set_strings: 1</t>
+  </si>
+  <si>
+    <t>control_knobs: 1</t>
+  </si>
+  <si>
+    <t>hardware_finish: 1</t>
+  </si>
+  <si>
+    <t>finish: 1</t>
+  </si>
+  <si>
+    <t>strings: 1</t>
+  </si>
+  <si>
+    <t>tailpiece: 1</t>
+  </si>
+  <si>
+    <t>pickguard: 1</t>
+  </si>
+  <si>
+    <t>truss_rod: 1</t>
+  </si>
+  <si>
+    <t>truss_rod_cover: 1</t>
+  </si>
+  <si>
+    <t>electronics_type: 1</t>
+  </si>
+  <si>
+    <t>output_jack: 1</t>
+  </si>
+  <si>
+    <t>onboard_electronics: 1</t>
+  </si>
+  <si>
+    <t>strings_gauge: 1</t>
+  </si>
+  <si>
+    <t>case: 1</t>
+  </si>
+  <si>
+    <t>zero_fret_type: 1</t>
+  </si>
+  <si>
+    <t>main_fret_type: 1</t>
+  </si>
+  <si>
+    <t>switch_tip: 1</t>
+  </si>
+  <si>
+    <t>neutral_fret: 1</t>
+  </si>
+  <si>
+    <t>switch_washer: 1</t>
+  </si>
+  <si>
+    <t>jack_plate_cover: 1</t>
+  </si>
+  <si>
+    <t>strap_buttons: 1</t>
+  </si>
+  <si>
+    <t>fretboard_side_dots: 1</t>
+  </si>
+  <si>
+    <t>string_lock: 1</t>
+  </si>
+  <si>
+    <t>knobs: 1</t>
+  </si>
+  <si>
+    <t>カラム候補</t>
+    <rPh sb="3" eb="5">
+      <t>コウホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>fingerboard</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>fret_count</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>pickups</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>joint</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>weight</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>color</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>maker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sub_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>maker_id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>maker_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>wood_id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>wood_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>wood_japanese_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>comment</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>code009</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギターメーカー名</t>
+    <rPh sb="7" eb="8">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Strandberg</t>
+  </si>
+  <si>
+    <t>SCHECTER</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木材名</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Maple</t>
+  </si>
+  <si>
+    <t>Mahogany</t>
+  </si>
+  <si>
+    <t>Alder</t>
+  </si>
+  <si>
+    <t>Ash</t>
+  </si>
+  <si>
+    <t>Basswood</t>
+  </si>
+  <si>
+    <t>Rosewood</t>
+  </si>
+  <si>
+    <t>Ebony</t>
+  </si>
+  <si>
+    <t>Walnut</t>
+  </si>
+  <si>
+    <t>Korina</t>
+  </si>
+  <si>
+    <t>Spruce</t>
+  </si>
+  <si>
+    <t>Cedar</t>
+  </si>
+  <si>
+    <t>Pau Ferro</t>
+  </si>
+  <si>
+    <t>Ovangkol</t>
+  </si>
+  <si>
+    <t>Koa</t>
+  </si>
+  <si>
+    <t>Poplar</t>
+  </si>
+  <si>
+    <t>Nato</t>
+  </si>
+  <si>
+    <t>Agathis</t>
+  </si>
+  <si>
+    <t>Bubinga</t>
+  </si>
+  <si>
+    <t>Wenge</t>
+  </si>
+  <si>
+    <t>Purpleheart</t>
+  </si>
+  <si>
+    <t>マホガニー</t>
+  </si>
+  <si>
+    <t>アルダー</t>
+  </si>
+  <si>
+    <t>パーフェロー</t>
+  </si>
+  <si>
+    <t>オバンコール</t>
+  </si>
+  <si>
+    <t>アガチス</t>
+  </si>
+  <si>
+    <t>ブビンガ</t>
+  </si>
+  <si>
+    <t>ウェンジ</t>
+  </si>
+  <si>
+    <t>パープルハート</t>
+  </si>
+  <si>
+    <t>メイプル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エボニー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウォルナット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コリーナ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スプルース</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シダー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ポプラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナトー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>硬くて明るい音。アタック強めでサスティン良好。</t>
+  </si>
+  <si>
+    <t>中低域が豊かで温かい音。レスポール系の定番。</t>
+  </si>
+  <si>
+    <t>バランスが良くクセが少ない。ストラト系の定番。</t>
+  </si>
+  <si>
+    <t>明るく抜ける音。スラップ向き。</t>
+  </si>
+  <si>
+    <t>軽くて扱いやすい。柔らかくウォームな音。</t>
+  </si>
+  <si>
+    <t>甘くて丸い音。指板材として定番。</t>
+  </si>
+  <si>
+    <t>硬くてタイト。高域がクリアでアタック強い。</t>
+  </si>
+  <si>
+    <t>中域が豊かで落ち着いたトーン。</t>
+  </si>
+  <si>
+    <t>マホガニーに似るが軽く、明るさもある。</t>
+  </si>
+  <si>
+    <t>軽くて響きが良い。アコギのトップ材の王道。</t>
+  </si>
+  <si>
+    <t>柔らかく温かい音。アコギでよく使われる。</t>
+  </si>
+  <si>
+    <t>ローズウッドに近いがやや明るい。</t>
+  </si>
+  <si>
+    <t>ローズウッド系の代替。中域が豊か。</t>
+  </si>
+  <si>
+    <t>明るく華やか。ウクレレで有名。</t>
+  </si>
+  <si>
+    <t>軽くて安価。音はやや平坦。</t>
+  </si>
+  <si>
+    <t>マホガニー系の代替材。コスパ良い。</t>
+  </si>
+  <si>
+    <t>柔らかく低価格帯で使用される。</t>
+  </si>
+  <si>
+    <t>硬く重い。低域が強くサスティン長い。</t>
+  </si>
+  <si>
+    <t>非常に硬くタイト。高域が強く個性的。</t>
+  </si>
+  <si>
+    <t>硬く鮮やかな音。アクセント材として使用。</t>
+  </si>
+  <si>
+    <t>code010</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アッシュ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バスウッド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ローズウッド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://jp.fender.com/collections/electric-guitars</t>
+  </si>
+  <si>
+    <t>https://jp.fender.com/collections/electric-guitars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://espguitars.co.jp/products/esp</t>
+  </si>
+  <si>
+    <t>統計</t>
+    <rPh sb="0" eb="2">
+      <t>トウケイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5517,7 +6439,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5553,8 +6475,14 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5582,6 +6510,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5662,7 +6596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5775,6 +6709,11 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -9468,7 +10407,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:P98"/>
+  <dimension ref="B3:P118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -9718,7 +10657,7 @@
         <v>122</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K12" s="18"/>
     </row>
@@ -10034,7 +10973,7 @@
         <v>122</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J23" s="18"/>
     </row>
@@ -10294,7 +11233,7 @@
         <v>122</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J33" s="18"/>
     </row>
@@ -10572,7 +11511,7 @@
         <v>122</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J43" s="18"/>
     </row>
@@ -10676,7 +11615,7 @@
         <v>122</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J47" s="18"/>
     </row>
@@ -11518,10 +12457,10 @@
         <v>122</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16">
       <c r="B81" s="43" t="s">
         <v>511</v>
       </c>
@@ -11547,7 +12486,7 @@
         <v>INSERT INTO m_code VALUES ('code007',1,'一般','一','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="82" spans="2:11">
+    <row r="82" spans="2:16">
       <c r="B82" s="43" t="s">
         <v>511</v>
       </c>
@@ -11573,7 +12512,7 @@
         <v>INSERT INTO m_code VALUES ('code007',2,'優良','優','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="83" spans="2:11">
+    <row r="83" spans="2:16">
       <c r="B83" s="43" t="s">
         <v>511</v>
       </c>
@@ -11599,7 +12538,7 @@
         <v>INSERT INTO m_code VALUES ('code007',3,'カモ','カ','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="84" spans="2:11">
+    <row r="84" spans="2:16">
       <c r="B84" s="43" t="s">
         <v>511</v>
       </c>
@@ -11625,7 +12564,7 @@
         <v>INSERT INTO m_code VALUES ('code007',4,'要注意','要','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="85" spans="2:11">
+    <row r="85" spans="2:16">
       <c r="B85" s="43" t="s">
         <v>511</v>
       </c>
@@ -11651,7 +12590,7 @@
         <v>INSERT INTO m_code VALUES ('code007',5,'ブラックリスト','ブ','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="86" spans="2:11">
+    <row r="86" spans="2:16">
       <c r="B86" s="43" t="s">
         <v>511</v>
       </c>
@@ -11677,7 +12616,7 @@
         <v>INSERT INTO m_code VALUES ('code007',90,'管理者','管','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="87" spans="2:11">
+    <row r="87" spans="2:16">
       <c r="B87" s="43" t="s">
         <v>511</v>
       </c>
@@ -11703,7 +12642,7 @@
         <v>INSERT INTO m_code VALUES ('code007',91,'統括管理者','統','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="88" spans="2:11">
+    <row r="88" spans="2:16">
       <c r="B88" s="6" t="s">
         <v>153</v>
       </c>
@@ -11726,10 +12665,10 @@
         <v>122</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16">
       <c r="B89" s="43" t="s">
         <v>1119</v>
       </c>
@@ -11753,7 +12692,7 @@
         <v>INSERT INTO m_code VALUES ('code008',1,'モンスター能力値','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="90" spans="2:11">
+    <row r="90" spans="2:16">
       <c r="B90" s="43" t="s">
         <v>1119</v>
       </c>
@@ -11777,7 +12716,7 @@
         <v>INSERT INTO m_code VALUES ('code008',2,'モンスタースキル','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="91" spans="2:11">
+    <row r="91" spans="2:16">
       <c r="B91" s="43" t="s">
         <v>1119</v>
       </c>
@@ -11801,14 +12740,749 @@
         <v>INSERT INTO m_code VALUES ('code008',3,'使用モンスター','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="97" spans="11:16">
-      <c r="P97" s="5">
+    <row r="92" spans="2:16">
+      <c r="B92" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="2:16">
+      <c r="B93" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8">
+        <v>1</v>
+      </c>
+      <c r="F93" s="8"/>
+      <c r="G93" s="9">
+        <v>0</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K93" s="5" t="str">
+        <f t="shared" ref="K93:K118" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code009',1,'ESP','','',0,0.0,'https://espguitars.co.jp/products/esp');</v>
+      </c>
+    </row>
+    <row r="94" spans="2:16">
+      <c r="B94" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8">
+        <v>2</v>
+      </c>
+      <c r="F94" s="8"/>
+      <c r="G94" s="9">
+        <v>0</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K94" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code009',2,'Fender','','',0,0.0,'https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB');</v>
+      </c>
+    </row>
+    <row r="95" spans="2:16">
+      <c r="B95" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8">
+        <v>3</v>
+      </c>
+      <c r="F95" s="8"/>
+      <c r="G95" s="9">
+        <v>0</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K95" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code009',3,'Gibson','','',0,0.0,'https://strandbergguitars.com/en-US/guitars');</v>
+      </c>
+    </row>
+    <row r="96" spans="2:16">
+      <c r="B96" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8">
+        <v>4</v>
+      </c>
+      <c r="F96" s="8"/>
+      <c r="G96" s="9">
+        <v>0</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>1464</v>
+      </c>
+      <c r="K96" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code009',4,'Strandberg','','',0,0.0,'https://jp.fender.com/collections/electric-guitars');</v>
+      </c>
+      <c r="P96" s="5">
         <v>444</v>
       </c>
     </row>
-    <row r="98" spans="11:16">
-      <c r="K98" s="5" t="s">
+    <row r="97" spans="2:11">
+      <c r="B97" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8">
+        <v>5</v>
+      </c>
+      <c r="F97" s="8"/>
+      <c r="G97" s="9">
+        <v>0</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K97" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code009',5,'SCHECTER','','',0,0.0,'https://schecter.co.jp/guitar/');</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8">
+        <v>1</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G99" s="9">
+        <v>0</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="K99" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',1,'Maple','','メイプル',0,0.0,'硬くて明るい音。アタック強めでサスティン良好。');</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8">
+        <v>2</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G100" s="9">
+        <v>0</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K100" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',2,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。レスポール系の定番。');</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8">
+        <v>3</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G101" s="9">
+        <v>0</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="K101" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',3,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。ストラト系の定番。');</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8">
+        <v>4</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G102" s="9">
+        <v>0</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K102" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',4,'Ash','','アッシュ',0,0.0,'明るく抜ける音。スラップ向き。');</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8">
+        <v>5</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G103" s="9">
+        <v>0</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K103" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',5,'Basswood','','バスウッド',0,0.0,'軽くて扱いやすい。柔らかくウォームな音。');</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8">
+        <v>6</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G104" s="9">
+        <v>0</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>1445</v>
+      </c>
+      <c r="K104" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',6,'Rosewood','','ローズウッド',0,0.0,'甘くて丸い音。指板材として定番。');</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="B105" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8">
         <v>7</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G105" s="9">
+        <v>0</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K105" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',7,'Ebony','','エボニー',0,0.0,'硬くてタイト。高域がクリアでアタック強い。');</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8">
+        <v>8</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G106" s="9">
+        <v>0</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K106" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',8,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8">
+        <v>9</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G107" s="9">
+        <v>0</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K107" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',9,'Korina','','コリーナ',0,0.0,'マホガニーに似るが軽く、明るさもある。');</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="B108" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8">
+        <v>10</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G108" s="9">
+        <v>0</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K108" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',10,'Spruce','','スプルース',0,0.0,'軽くて響きが良い。アコギのトップ材の王道。');</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8">
+        <v>11</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G109" s="9">
+        <v>0</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K109" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',11,'Cedar','','シダー',0,0.0,'柔らかく温かい音。アコギでよく使われる。');</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8">
+        <v>12</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G110" s="9">
+        <v>0</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>1451</v>
+      </c>
+      <c r="K110" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',12,'Pau Ferro','','パーフェロー',0,0.0,'ローズウッドに近いがやや明るい。');</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8">
+        <v>13</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G111" s="9">
+        <v>0</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="K111" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',13,'Ovangkol','','オバンコール',0,0.0,'ローズウッド系の代替。中域が豊か。');</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="B112" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8">
+        <v>14</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G112" s="9">
+        <v>0</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K112" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',14,'Koa','','コア',0,0.0,'明るく華やか。ウクレレで有名。');</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
+      <c r="B113" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8">
+        <v>15</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G113" s="9">
+        <v>0</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K113" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽くて安価。音はやや平坦。');</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
+      <c r="B114" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8">
+        <v>16</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G114" s="9">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K114" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',16,'Nato','','ナトー',0,0.0,'マホガニー系の代替材。コスパ良い。');</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11">
+      <c r="B115" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8">
+        <v>17</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G115" s="9">
+        <v>0</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="K115" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',17,'Agathis','','アガチス',0,0.0,'柔らかく低価格帯で使用される。');</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11">
+      <c r="B116" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8">
+        <v>18</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G116" s="9">
+        <v>0</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>1457</v>
+      </c>
+      <c r="K116" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',18,'Bubinga','','ブビンガ',0,0.0,'硬く重い。低域が強くサスティン長い。');</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11">
+      <c r="B117" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8">
+        <v>19</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G117" s="9">
+        <v>0</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K117" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',19,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイト。高域が強く個性的。');</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11">
+      <c r="B118" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8">
+        <v>20</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G118" s="9">
+        <v>0</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>1459</v>
+      </c>
+      <c r="K118" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>INSERT INTO m_code VALUES ('code010',20,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかな音。アクセント材として使用。');</v>
       </c>
     </row>
   </sheetData>
@@ -15365,7 +17039,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -15398,7 +17072,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -15431,7 +17105,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -15461,7 +17135,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -15494,7 +17168,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -15524,7 +17198,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -15557,7 +17231,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -15587,7 +17261,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -15620,7 +17294,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -15653,7 +17327,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -15683,7 +17357,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -15716,7 +17390,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -15749,7 +17423,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -15779,7 +17453,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -15812,7 +17486,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -15842,7 +17516,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -15875,7 +17549,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -15908,7 +17582,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -15938,7 +17612,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -15971,7 +17645,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -16004,7 +17678,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -16034,7 +17708,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -16067,7 +17741,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -16097,7 +17771,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -16130,7 +17804,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -16160,7 +17834,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -16193,7 +17867,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -16226,7 +17900,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -16259,7 +17933,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -16289,7 +17963,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -16322,7 +17996,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -16355,7 +18029,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -16385,7 +18059,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -16418,7 +18092,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -16451,7 +18125,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -16482,7 +18156,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -16515,7 +18189,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -16548,7 +18222,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -16581,7 +18255,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -16611,7 +18285,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -16644,7 +18318,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -16677,7 +18351,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -16707,7 +18381,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -16740,7 +18414,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -16773,7 +18447,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -16803,7 +18477,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -16836,7 +18510,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -16869,7 +18543,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -16899,7 +18573,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -16929,7 +18603,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -16959,7 +18633,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -16989,7 +18663,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -17019,7 +18693,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -17052,7 +18726,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -17085,7 +18759,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -17115,7 +18789,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -17145,7 +18819,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -17175,7 +18849,7 @@
         <v>299</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -17208,7 +18882,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -17241,7 +18915,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -17271,7 +18945,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -17304,7 +18978,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -17337,7 +19011,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -17370,7 +19044,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -17400,7 +19074,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -17430,7 +19104,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -17460,7 +19134,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -17490,7 +19164,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -17520,7 +19194,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -17550,7 +19224,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -17580,7 +19254,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -17610,7 +19284,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -17640,7 +19314,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -17670,7 +19344,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -17700,7 +19374,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -17730,7 +19404,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -17760,7 +19434,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -17792,7 +19466,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -17824,7 +19498,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -17854,7 +19528,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -17887,7 +19561,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -17920,7 +19594,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -17950,7 +19624,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -17980,7 +19654,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$100,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>
@@ -35461,13 +37135,940 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:K79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:11">
+      <c r="B2" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="59" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="13.2">
+      <c r="B5" s="58" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="13.2">
+      <c r="B6" s="58" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="13.2">
+      <c r="B7" s="58" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="13.2">
+      <c r="B8" s="58" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="13.2">
+      <c r="B9" s="58" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="13.2">
+      <c r="B10" s="58" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="13.2">
+      <c r="B11" s="58" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="13.2">
+      <c r="B12" s="58" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="13.2">
+      <c r="B13" s="58" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="13.2">
+      <c r="B14" s="58" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="13.2">
+      <c r="B15" s="58" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="13.2">
+      <c r="B16" s="58" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="13.2">
+      <c r="B17" s="58" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="13.2">
+      <c r="B18" s="58" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="13.2">
+      <c r="B19" s="58" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="13.2">
+      <c r="B20" s="58" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="C21" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="C22" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="C23" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="C24" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="C25" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="C26" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="C27" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="C28" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="C29" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="C30" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="C31" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="C32" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8">
+      <c r="C35" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8">
+      <c r="C36" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8">
+      <c r="C39" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8">
+      <c r="C40" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8">
+      <c r="C41" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8">
+      <c r="D42" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8">
+      <c r="D43" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8">
+      <c r="D44" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8">
+      <c r="D45" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8">
+      <c r="D46" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8">
+      <c r="D47" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8">
+      <c r="D48" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8">
+      <c r="D49" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8">
+      <c r="D50" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8">
+      <c r="D51" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8">
+      <c r="D52" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8">
+      <c r="D53" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8">
+      <c r="D54" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8">
+      <c r="D55" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8">
+      <c r="D56" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8">
+      <c r="D57" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8">
+      <c r="D58" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8">
+      <c r="D59" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8">
+      <c r="D60" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8">
+      <c r="D61" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8">
+      <c r="D62" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8">
+      <c r="H63" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8">
+      <c r="H64" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8">
+      <c r="H65" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="66" spans="8:8">
+      <c r="H66" s="1" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="67" spans="8:8">
+      <c r="H67" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="68" spans="8:8">
+      <c r="H68" s="1" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="69" spans="8:8">
+      <c r="H69" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="70" spans="8:8">
+      <c r="H70" s="1" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="71" spans="8:8">
+      <c r="H71" s="1" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="72" spans="8:8">
+      <c r="H72" s="1" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="73" spans="8:8">
+      <c r="H73" s="1" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="74" spans="8:8">
+      <c r="H74" s="1" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8">
+      <c r="H75" s="1" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
+      <c r="H76" s="1" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8">
+      <c r="H77" s="1" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8">
+      <c r="H78" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8">
+      <c r="H79" s="1" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J10:J24">
+    <sortCondition ref="J24"/>
+  </sortState>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{36F1793A-29C9-405A-842F-63D38582F0C1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90A2938-CF47-4C90-A0DF-D3072D7F35D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C0572-E3D4-481E-BFD0-AA71E10E64BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="1469">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6429,6 +6429,10 @@
     <rPh sb="0" eb="2">
       <t>トウケイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>series</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -37618,7 +37622,7 @@
         <v>1325</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1386</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -37630,6 +37634,9 @@
       </c>
       <c r="H25" s="1" t="s">
         <v>1326</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>1386</v>
       </c>
     </row>
     <row r="26" spans="2:10">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C0572-E3D4-481E-BFD0-AA71E10E64BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94DA16E-3818-483E-88DE-BE764AD4CF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="1469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3522" uniqueCount="1508">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6163,10 +6163,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>sub_name</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>maker_id</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6252,9 +6248,6 @@
     <t>Cedar</t>
   </si>
   <si>
-    <t>Pau Ferro</t>
-  </si>
-  <si>
     <t>Ovangkol</t>
   </si>
   <si>
@@ -6303,115 +6296,10 @@
     <t>パープルハート</t>
   </si>
   <si>
-    <t>メイプル</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エボニー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ウォルナット</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>コリーナ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スプルース</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>シダー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>コア</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ポプラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ナトー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>硬くて明るい音。アタック強めでサスティン良好。</t>
-  </si>
-  <si>
-    <t>中低域が豊かで温かい音。レスポール系の定番。</t>
-  </si>
-  <si>
-    <t>バランスが良くクセが少ない。ストラト系の定番。</t>
-  </si>
-  <si>
-    <t>明るく抜ける音。スラップ向き。</t>
-  </si>
-  <si>
-    <t>軽くて扱いやすい。柔らかくウォームな音。</t>
-  </si>
-  <si>
-    <t>甘くて丸い音。指板材として定番。</t>
-  </si>
-  <si>
-    <t>硬くてタイト。高域がクリアでアタック強い。</t>
-  </si>
-  <si>
     <t>中域が豊かで落ち着いたトーン。</t>
   </si>
   <si>
-    <t>マホガニーに似るが軽く、明るさもある。</t>
-  </si>
-  <si>
-    <t>軽くて響きが良い。アコギのトップ材の王道。</t>
-  </si>
-  <si>
-    <t>柔らかく温かい音。アコギでよく使われる。</t>
-  </si>
-  <si>
-    <t>ローズウッドに近いがやや明るい。</t>
-  </si>
-  <si>
-    <t>ローズウッド系の代替。中域が豊か。</t>
-  </si>
-  <si>
-    <t>明るく華やか。ウクレレで有名。</t>
-  </si>
-  <si>
-    <t>軽くて安価。音はやや平坦。</t>
-  </si>
-  <si>
-    <t>マホガニー系の代替材。コスパ良い。</t>
-  </si>
-  <si>
-    <t>柔らかく低価格帯で使用される。</t>
-  </si>
-  <si>
-    <t>硬く重い。低域が強くサスティン長い。</t>
-  </si>
-  <si>
-    <t>非常に硬くタイト。高域が強く個性的。</t>
-  </si>
-  <si>
-    <t>硬く鮮やかな音。アクセント材として使用。</t>
-  </si>
-  <si>
     <t>code010</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アッシュ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>バスウッド</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ローズウッド</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -6433,6 +6321,228 @@
   </si>
   <si>
     <t>series</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>src</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>？？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>HardMaple</t>
+  </si>
+  <si>
+    <t>FlameMaple</t>
+  </si>
+  <si>
+    <t>QuiltedMaple</t>
+  </si>
+  <si>
+    <t>BirdseyeMaple</t>
+  </si>
+  <si>
+    <t>RoastedMaple</t>
+  </si>
+  <si>
+    <t>HonduranMahogany</t>
+  </si>
+  <si>
+    <t>Sapele</t>
+  </si>
+  <si>
+    <t>WhiteKorina</t>
+  </si>
+  <si>
+    <t>IndianRosewood</t>
+  </si>
+  <si>
+    <t>BrazilianRosewood</t>
+  </si>
+  <si>
+    <t>PauFerro</t>
+  </si>
+  <si>
+    <t>Padauk</t>
+  </si>
+  <si>
+    <t>Zebrawood</t>
+  </si>
+  <si>
+    <t>メイプル</t>
+  </si>
+  <si>
+    <t>ハードメイプル</t>
+  </si>
+  <si>
+    <t>フレイムメイプル</t>
+  </si>
+  <si>
+    <t>キルテッドメイプル</t>
+  </si>
+  <si>
+    <t>バーズアイメイプル</t>
+  </si>
+  <si>
+    <t>ローステッドメイプル</t>
+  </si>
+  <si>
+    <t>ホンジュラスマホガニー</t>
+  </si>
+  <si>
+    <t>サペリ</t>
+  </si>
+  <si>
+    <t>コリーナ</t>
+  </si>
+  <si>
+    <t>ホワイトコリーナ</t>
+  </si>
+  <si>
+    <t>アッシュ</t>
+  </si>
+  <si>
+    <t>バスウッド</t>
+  </si>
+  <si>
+    <t>ポプラ</t>
+  </si>
+  <si>
+    <t>スプルース</t>
+  </si>
+  <si>
+    <t>シダー</t>
+  </si>
+  <si>
+    <t>ローズウッド</t>
+  </si>
+  <si>
+    <t>インディアンローズウッド</t>
+  </si>
+  <si>
+    <t>ブラジリアンローズウッド</t>
+  </si>
+  <si>
+    <t>エボニー</t>
+  </si>
+  <si>
+    <t>ウォルナット</t>
+  </si>
+  <si>
+    <t>パドゥーク</t>
+  </si>
+  <si>
+    <t>コア</t>
+  </si>
+  <si>
+    <t>ナトー</t>
+  </si>
+  <si>
+    <t>ゼブラウッド</t>
+  </si>
+  <si>
+    <t>明るくハリがあり、アタックが強い。</t>
+  </si>
+  <si>
+    <t>硬質でタイト、明瞭なアタック。</t>
+  </si>
+  <si>
+    <t>明るく抜けが良く、華やかな倍音。</t>
+  </si>
+  <si>
+    <t>立体的で広がりがあり、煌びやかな響き。</t>
+  </si>
+  <si>
+    <t>粒立ちが良く、明るくシャープ。</t>
+  </si>
+  <si>
+    <t>引き締まったタイトな音で反応が速い。</t>
+  </si>
+  <si>
+    <t>中低域が豊かで温かい音。</t>
+  </si>
+  <si>
+    <t>深みがあり、太くリッチな中低域。</t>
+  </si>
+  <si>
+    <t>温かく柔らかいトーンでバランスが良い。</t>
+  </si>
+  <si>
+    <t>中域が豊かで太い音。</t>
+  </si>
+  <si>
+    <t>明るく抜けが良く、軽快なレスポンス。</t>
+  </si>
+  <si>
+    <t>バランスが良くクセが少ない。</t>
+  </si>
+  <si>
+    <t>明るく抜ける音でアタックが強い。</t>
+  </si>
+  <si>
+    <t>軽く柔らかく、ウォームで扱いやすい。</t>
+  </si>
+  <si>
+    <t>軽く素直でクセが少ない。</t>
+  </si>
+  <si>
+    <t>軽く響きが良く、明るいトーン。</t>
+  </si>
+  <si>
+    <t>柔らかく温かい音。</t>
+  </si>
+  <si>
+    <t>甘く丸い音で中域が豊か。</t>
+  </si>
+  <si>
+    <t>甘く深みがあり、豊かな中低域。</t>
+  </si>
+  <si>
+    <t>濃厚で深いトーン、豊かな倍音。</t>
+  </si>
+  <si>
+    <t>明るく硬質でタイトな音。</t>
+  </si>
+  <si>
+    <t>中域が豊かで温かいトーン。</t>
+  </si>
+  <si>
+    <t>硬くタイトで高域がクリア。</t>
+  </si>
+  <si>
+    <t>明るく抜けが良く、個性的な響き。</t>
+  </si>
+  <si>
+    <t>明るく華やかで軽快。</t>
+  </si>
+  <si>
+    <t>中低域が豊かで温かい。</t>
+  </si>
+  <si>
+    <t>柔らかくウォームで素直。</t>
+  </si>
+  <si>
+    <t>重く硬質でサスティンが長い。</t>
+  </si>
+  <si>
+    <t>非常に硬くタイトで個性的。</t>
+  </si>
+  <si>
+    <t>硬く鮮やかでアタックが強い。</t>
+  </si>
+  <si>
+    <t>明るく硬質でクセのあるトーン。</t>
+  </si>
+  <si>
+    <t>省略</t>
+    <rPh sb="0" eb="2">
+      <t>ショウリャク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10411,7 +10521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:P118"/>
+  <dimension ref="B3:L132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -12464,7 +12574,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="81" spans="2:16">
+    <row r="81" spans="2:11">
       <c r="B81" s="43" t="s">
         <v>511</v>
       </c>
@@ -12490,7 +12600,7 @@
         <v>INSERT INTO m_code VALUES ('code007',1,'一般','一','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="82" spans="2:16">
+    <row r="82" spans="2:11">
       <c r="B82" s="43" t="s">
         <v>511</v>
       </c>
@@ -12516,7 +12626,7 @@
         <v>INSERT INTO m_code VALUES ('code007',2,'優良','優','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="83" spans="2:16">
+    <row r="83" spans="2:11">
       <c r="B83" s="43" t="s">
         <v>511</v>
       </c>
@@ -12542,7 +12652,7 @@
         <v>INSERT INTO m_code VALUES ('code007',3,'カモ','カ','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="84" spans="2:16">
+    <row r="84" spans="2:11">
       <c r="B84" s="43" t="s">
         <v>511</v>
       </c>
@@ -12568,7 +12678,7 @@
         <v>INSERT INTO m_code VALUES ('code007',4,'要注意','要','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="85" spans="2:16">
+    <row r="85" spans="2:11">
       <c r="B85" s="43" t="s">
         <v>511</v>
       </c>
@@ -12594,7 +12704,7 @@
         <v>INSERT INTO m_code VALUES ('code007',5,'ブラックリスト','ブ','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="86" spans="2:16">
+    <row r="86" spans="2:11">
       <c r="B86" s="43" t="s">
         <v>511</v>
       </c>
@@ -12620,7 +12730,7 @@
         <v>INSERT INTO m_code VALUES ('code007',90,'管理者','管','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="87" spans="2:16">
+    <row r="87" spans="2:11">
       <c r="B87" s="43" t="s">
         <v>511</v>
       </c>
@@ -12646,7 +12756,7 @@
         <v>INSERT INTO m_code VALUES ('code007',91,'統括管理者','統','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="88" spans="2:16">
+    <row r="88" spans="2:11">
       <c r="B88" s="6" t="s">
         <v>153</v>
       </c>
@@ -12672,7 +12782,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="89" spans="2:16">
+    <row r="89" spans="2:11">
       <c r="B89" s="43" t="s">
         <v>1119</v>
       </c>
@@ -12696,7 +12806,7 @@
         <v>INSERT INTO m_code VALUES ('code008',1,'モンスター能力値','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="90" spans="2:16">
+    <row r="90" spans="2:11">
       <c r="B90" s="43" t="s">
         <v>1119</v>
       </c>
@@ -12720,7 +12830,7 @@
         <v>INSERT INTO m_code VALUES ('code008',2,'モンスタースキル','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="91" spans="2:16">
+    <row r="91" spans="2:11">
       <c r="B91" s="43" t="s">
         <v>1119</v>
       </c>
@@ -12744,12 +12854,12 @@
         <v>INSERT INTO m_code VALUES ('code008',3,'使用モンスター','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="92" spans="2:16">
+    <row r="92" spans="2:11">
       <c r="B92" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>1127</v>
@@ -12770,9 +12880,9 @@
         <v>133</v>
       </c>
     </row>
-    <row r="93" spans="2:16">
+    <row r="93" spans="2:11">
       <c r="B93" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>1184</v>
@@ -12789,16 +12899,16 @@
         <v>125</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>1466</v>
+        <v>1433</v>
       </c>
       <c r="K93" s="5" t="str">
-        <f t="shared" ref="K93:K118" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K93:K97" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code009',1,'ESP','','',0,0.0,'https://espguitars.co.jp/products/esp');</v>
       </c>
     </row>
-    <row r="94" spans="2:16">
+    <row r="94" spans="2:11">
       <c r="B94" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>1292</v>
@@ -12815,16 +12925,16 @@
         <v>125</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>1289</v>
+        <v>1431</v>
       </c>
       <c r="K94" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code009',2,'Fender','','',0,0.0,'https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB');</v>
-      </c>
-    </row>
-    <row r="95" spans="2:16">
+        <v>INSERT INTO m_code VALUES ('code009',2,'Fender','','',0,0.0,'https://jp.fender.com/collections/electric-guitars');</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
       <c r="B95" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>1198</v>
@@ -12841,19 +12951,19 @@
         <v>125</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>1239</v>
+        <v>1289</v>
       </c>
       <c r="K95" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code009',3,'Gibson','','',0,0.0,'https://strandbergguitars.com/en-US/guitars');</v>
-      </c>
-    </row>
-    <row r="96" spans="2:16">
+        <v>INSERT INTO m_code VALUES ('code009',3,'Gibson','','',0,0.0,'https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB');</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
       <c r="B96" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8">
@@ -12867,19 +12977,16 @@
         <v>125</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>1464</v>
+        <v>1239</v>
       </c>
       <c r="K96" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code009',4,'Strandberg','','',0,0.0,'https://jp.fender.com/collections/electric-guitars');</v>
-      </c>
-      <c r="P96" s="5">
-        <v>444</v>
+        <v>INSERT INTO m_code VALUES ('code009',4,'Strandberg','','',0,0.0,'https://strandbergguitars.com/en-US/guitars');</v>
       </c>
     </row>
     <row r="97" spans="2:11">
       <c r="B97" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>1301</v>
@@ -12908,7 +13015,7 @@
         <v>153</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>1127</v>
@@ -12931,17 +13038,17 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>1403</v>
+        <v>1438</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="G99" s="9">
         <v>0</v>
@@ -12949,27 +13056,25 @@
       <c r="H99" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I99" s="8" t="s">
-        <v>1440</v>
-      </c>
+      <c r="I99" s="8"/>
       <c r="K99" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',1,'Maple','','メイプル',0,0.0,'硬くて明るい音。アタック強めでサスティン良好。');</v>
+        <f t="shared" ref="K99:K131" si="12">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B99&amp;"'"&amp;","&amp;E99&amp;","&amp;"'"&amp;C99&amp;"'"&amp;","&amp;"'"&amp;D99&amp;"'"&amp;","&amp;"'"&amp;F99&amp;"'"&amp;","&amp;G99&amp;","&amp;H99&amp;","&amp;"'"&amp;I99&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1404</v>
+        <v>1439</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="G100" s="9">
         <v>0</v>
@@ -12978,26 +13083,26 @@
         <v>125</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>1441</v>
+        <v>1477</v>
       </c>
       <c r="K100" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',2,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。レスポール系の定番。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1405</v>
+        <v>1440</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>1424</v>
+        <v>1454</v>
       </c>
       <c r="G101" s="9">
         <v>0</v>
@@ -13006,26 +13111,26 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1442</v>
+        <v>1478</v>
       </c>
       <c r="K101" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',3,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。ストラト系の定番。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1406</v>
+        <v>1441</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="G102" s="9">
         <v>0</v>
@@ -13034,26 +13139,26 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1443</v>
+        <v>1479</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',4,'Ash','','アッシュ',0,0.0,'明るく抜ける音。スラップ向き。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1407</v>
+        <v>1442</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G103" s="9">
         <v>0</v>
@@ -13062,26 +13167,26 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1444</v>
+        <v>1480</v>
       </c>
       <c r="K103" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',5,'Basswood','','バスウッド',0,0.0,'軽くて扱いやすい。柔らかくウォームな音。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1408</v>
+        <v>1443</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="G104" s="9">
         <v>0</v>
@@ -13090,26 +13195,26 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1445</v>
+        <v>1481</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',6,'Rosewood','','ローズウッド',0,0.0,'甘くて丸い音。指板材として定番。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>1432</v>
+        <v>1452</v>
       </c>
       <c r="G105" s="9">
         <v>0</v>
@@ -13118,26 +13223,26 @@
         <v>125</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>1446</v>
+        <v>1476</v>
       </c>
       <c r="K105" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',7,'Ebony','','エボニー',0,0.0,'硬くてタイト。高域がクリアでアタック強い。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1410</v>
+        <v>1444</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1433</v>
+        <v>1458</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
@@ -13146,26 +13251,26 @@
         <v>125</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>1447</v>
+        <v>1483</v>
       </c>
       <c r="K106" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',8,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1434</v>
+        <v>1421</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -13174,26 +13279,26 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1448</v>
+        <v>1482</v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',9,'Korina','','コリーナ',0,0.0,'マホガニーに似るが軽く、明るさもある。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1412</v>
+        <v>1445</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1435</v>
+        <v>1459</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -13202,26 +13307,26 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1449</v>
+        <v>1484</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',10,'Spruce','','スプルース',0,0.0,'軽くて響きが良い。アコギのトップ材の王道。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1436</v>
+        <v>1460</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -13230,26 +13335,26 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1450</v>
+        <v>1485</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',11,'Cedar','','シダー',0,0.0,'柔らかく温かい音。アコギでよく使われる。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1414</v>
+        <v>1446</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1425</v>
+        <v>1461</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -13258,26 +13363,26 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1451</v>
+        <v>1486</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',12,'Pau Ferro','','パーフェロー',0,0.0,'ローズウッドに近いがやや明るい。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1415</v>
+        <v>1404</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -13286,26 +13391,26 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1452</v>
+        <v>1487</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',13,'Ovangkol','','オバンコール',0,0.0,'ローズウッド系の代替。中域が豊か。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1416</v>
+        <v>1405</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1437</v>
+        <v>1462</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -13314,26 +13419,26 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1453</v>
+        <v>1488</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',14,'Koa','','コア',0,0.0,'明るく華やか。ウクレレで有名。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1438</v>
+        <v>1463</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -13342,26 +13447,26 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1454</v>
+        <v>1489</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽くて安価。音はやや平坦。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1439</v>
+        <v>1464</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -13370,26 +13475,26 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1455</v>
+        <v>1490</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',16,'Nato','','ナトー',0,0.0,'マホガニー系の代替材。コスパ良い。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1427</v>
+        <v>1465</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -13398,26 +13503,26 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1456</v>
+        <v>1491</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',17,'Agathis','','アガチス',0,0.0,'柔らかく低価格帯で使用される。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1428</v>
+        <v>1466</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -13426,26 +13531,26 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1457</v>
+        <v>1492</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',18,'Bubinga','','ブビンガ',0,0.0,'硬く重い。低域が強くサスティン長い。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1421</v>
+        <v>1447</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1429</v>
+        <v>1468</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -13454,26 +13559,26 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1458</v>
+        <v>1494</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',19,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイト。高域が強く個性的。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="8" t="s">
-        <v>1460</v>
+        <v>1430</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1422</v>
+        <v>1448</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1430</v>
+        <v>1469</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -13482,11 +13587,401 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1459</v>
+        <v>1495</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code010',20,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかな音。アクセント材として使用。');</v>
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11">
+      <c r="B119" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8">
+        <v>20</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G119" s="9">
+        <v>0</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K119" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11">
+      <c r="B120" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8">
+        <v>21</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G120" s="9">
+        <v>0</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K120" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11">
+      <c r="B121" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8">
+        <v>22</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G121" s="9">
+        <v>0</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>1497</v>
+      </c>
+      <c r="K121" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11">
+      <c r="B122" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8">
+        <v>23</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G122" s="9">
+        <v>0</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>1498</v>
+      </c>
+      <c r="K122" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11">
+      <c r="B123" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8">
+        <v>24</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G123" s="9">
+        <v>0</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="K123" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11">
+      <c r="B124" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8">
+        <v>25</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G124" s="9">
+        <v>0</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>1499</v>
+      </c>
+      <c r="K124" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11">
+      <c r="B125" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8">
+        <v>26</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G125" s="9">
+        <v>0</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K125" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11">
+      <c r="B126" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8">
+        <v>27</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G126" s="9">
+        <v>0</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K126" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11">
+      <c r="B127" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8">
+        <v>28</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G127" s="9">
+        <v>0</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>1502</v>
+      </c>
+      <c r="K127" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11">
+      <c r="B128" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8">
+        <v>29</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G128" s="9">
+        <v>0</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K128" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+      </c>
+    </row>
+    <row r="129" spans="2:11">
+      <c r="B129" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D129" s="8"/>
+      <c r="E129" s="8">
+        <v>30</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G129" s="9">
+        <v>0</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>1504</v>
+      </c>
+      <c r="K129" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+      </c>
+    </row>
+    <row r="130" spans="2:11">
+      <c r="B130" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8">
+        <v>31</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G130" s="9">
+        <v>0</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>1505</v>
+      </c>
+      <c r="K130" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+      </c>
+    </row>
+    <row r="131" spans="2:11">
+      <c r="B131" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8">
+        <v>32</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G131" s="9">
+        <v>0</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K131" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code010',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+      </c>
+    </row>
+    <row r="132" spans="2:11">
+      <c r="B132" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8">
+        <v>99</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G132" s="9">
+        <v>0</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I132" s="8"/>
+      <c r="K132" s="5" t="str">
+        <f t="shared" ref="K132" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B132&amp;"'"&amp;","&amp;E132&amp;","&amp;"'"&amp;C132&amp;"'"&amp;","&amp;"'"&amp;D132&amp;"'"&amp;","&amp;"'"&amp;F132&amp;"'"&amp;","&amp;G132&amp;","&amp;H132&amp;","&amp;"'"&amp;I132&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
       </c>
     </row>
   </sheetData>
@@ -37166,7 +37661,7 @@
         <v>1292</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>1306</v>
@@ -37186,7 +37681,7 @@
         <v>1239</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>1465</v>
+        <v>1432</v>
       </c>
       <c r="F4" s="60" t="s">
         <v>1302</v>
@@ -37232,7 +37727,7 @@
         <v>1185</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1467</v>
+        <v>1434</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>1381</v>
@@ -37261,7 +37756,7 @@
         <v>1389</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13.2">
@@ -37287,7 +37782,7 @@
         <v>1390</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.2">
@@ -37310,7 +37805,7 @@
         <v>1310</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1391</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="13.2">
@@ -37333,10 +37828,10 @@
         <v>1311</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="13.2">
@@ -37359,10 +37854,10 @@
         <v>1312</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1204</v>
+        <v>1195</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="13.2">
@@ -37385,10 +37880,10 @@
         <v>1313</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1195</v>
+        <v>1387</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="13.2">
@@ -37411,7 +37906,7 @@
         <v>1314</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1387</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.2">
@@ -37434,7 +37929,7 @@
         <v>1315</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1197</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.2">
@@ -37457,7 +37952,7 @@
         <v>1316</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1397</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.2">
@@ -37477,7 +37972,7 @@
         <v>1317</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="13.2">
@@ -37497,7 +37992,7 @@
         <v>1318</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1383</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="13.2">
@@ -37517,7 +38012,7 @@
         <v>1319</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1217</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="13.2">
@@ -37537,7 +38032,7 @@
         <v>1320</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1385</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="13.2">
@@ -37557,7 +38052,7 @@
         <v>1321</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1254</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -37574,7 +38069,7 @@
         <v>1322</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -37591,7 +38086,7 @@
         <v>1323</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1388</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -37608,7 +38103,7 @@
         <v>1324</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1209</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -37622,7 +38117,7 @@
         <v>1325</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1468</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -38069,8 +38564,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J10:J24">
-    <sortCondition ref="J24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J9:J23">
+    <sortCondition ref="J23"/>
   </sortState>
   <phoneticPr fontId="2"/>
   <hyperlinks>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191D6E75-5618-46B0-B18B-48C6C72F2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C321C2C-A85A-4541-9ECF-A395726CC59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="1556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1557">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6194,9 +6194,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Strandberg</t>
-  </si>
-  <si>
     <t>SCHECTER</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6774,6 +6771,23 @@
   </si>
   <si>
     <t>https://espguitars.co.jp/signatureseries/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>.strandberg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>正式名称は.strandberg*　*がwindowsのファイル名としてアウト</t>
+    <rPh sb="0" eb="2">
+      <t>セイシキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10785,7 +10799,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="6" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1153</v>
@@ -10993,7 +11007,7 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="6" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1154</v>
@@ -11309,7 +11323,7 @@
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="6" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1155</v>
@@ -11569,7 +11583,7 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="6" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>1156</v>
@@ -11847,7 +11861,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="6" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>1157</v>
@@ -11951,7 +11965,7 @@
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="6" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>1158</v>
@@ -12793,7 +12807,7 @@
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="6" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>1159</v>
@@ -13001,7 +13015,7 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="6" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>1160</v>
@@ -13099,7 +13113,7 @@
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="6" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>1397</v>
@@ -13142,7 +13156,7 @@
         <v>125</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="K93" s="5" t="str">
         <f t="shared" ref="K93:K98" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
@@ -13168,7 +13182,7 @@
         <v>125</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="K94" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13206,7 +13220,7 @@
         <v>1396</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1398</v>
+        <v>1555</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8">
@@ -13222,9 +13236,12 @@
       <c r="I96" s="8" t="s">
         <v>1238</v>
       </c>
+      <c r="J96" s="5" t="s">
+        <v>1556</v>
+      </c>
       <c r="K96" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code009',4,'Strandberg','','',0,0.0,'https://strandbergguitars.com/en-US/guitars');</v>
+        <v>INSERT INTO m_code VALUES ('code009',4,'.strandberg','','',0,0.0,'https://strandbergguitars.com/en-US/guitars');</v>
       </c>
     </row>
     <row r="97" spans="2:11">
@@ -13258,7 +13275,7 @@
         <v>1396</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8">
@@ -13272,7 +13289,7 @@
         <v>125</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="K98" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13281,10 +13298,10 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="6" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>1126</v>
@@ -13307,17 +13324,17 @@
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8">
         <v>0</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="G100" s="9">
         <v>0</v>
@@ -13333,17 +13350,17 @@
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8">
         <v>1</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G101" s="9">
         <v>0</v>
@@ -13352,7 +13369,7 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K101" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13361,17 +13378,17 @@
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8">
         <v>2</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="G102" s="9">
         <v>0</v>
@@ -13380,7 +13397,7 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K102" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13389,17 +13406,17 @@
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
         <v>3</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G103" s="9">
         <v>0</v>
@@ -13408,7 +13425,7 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K103" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13417,17 +13434,17 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
         <v>4</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G104" s="9">
         <v>0</v>
@@ -13436,7 +13453,7 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="K104" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13445,17 +13462,17 @@
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8">
         <v>5</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G105" s="9">
         <v>0</v>
@@ -13464,7 +13481,7 @@
         <v>125</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="K105" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13473,17 +13490,17 @@
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
         <v>6</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
@@ -13492,7 +13509,7 @@
         <v>125</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K106" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13501,17 +13518,17 @@
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
         <v>7</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -13520,7 +13537,7 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="K107" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13529,17 +13546,17 @@
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
         <v>8</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -13548,7 +13565,7 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K108" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13557,17 +13574,17 @@
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
         <v>9</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -13576,7 +13593,7 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K109" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13585,17 +13602,17 @@
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
         <v>10</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -13604,7 +13621,7 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K110" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13613,17 +13630,17 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
         <v>11</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -13632,7 +13649,7 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13641,17 +13658,17 @@
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
         <v>12</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -13660,7 +13677,7 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13669,17 +13686,17 @@
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
         <v>13</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -13688,7 +13705,7 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13697,17 +13714,17 @@
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
         <v>14</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -13716,7 +13733,7 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13725,17 +13742,17 @@
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
         <v>15</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -13744,7 +13761,7 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13753,17 +13770,17 @@
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
         <v>16</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -13772,7 +13789,7 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13781,17 +13798,17 @@
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
         <v>17</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -13800,7 +13817,7 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13809,17 +13826,17 @@
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
         <v>18</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -13828,7 +13845,7 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13837,17 +13854,17 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
         <v>19</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -13856,7 +13873,7 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13865,17 +13882,17 @@
     </row>
     <row r="120" spans="2:11">
       <c r="B120" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
         <v>20</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -13884,7 +13901,7 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13893,17 +13910,17 @@
     </row>
     <row r="121" spans="2:11">
       <c r="B121" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
         <v>21</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -13912,7 +13929,7 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13921,17 +13938,17 @@
     </row>
     <row r="122" spans="2:11">
       <c r="B122" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
         <v>22</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -13940,7 +13957,7 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13949,17 +13966,17 @@
     </row>
     <row r="123" spans="2:11">
       <c r="B123" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
         <v>23</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -13968,7 +13985,7 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13977,17 +13994,17 @@
     </row>
     <row r="124" spans="2:11">
       <c r="B124" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
         <v>24</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -13996,7 +14013,7 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14005,17 +14022,17 @@
     </row>
     <row r="125" spans="2:11">
       <c r="B125" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
         <v>25</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -14024,7 +14041,7 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14033,17 +14050,17 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
         <v>26</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -14052,7 +14069,7 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14061,17 +14078,17 @@
     </row>
     <row r="127" spans="2:11">
       <c r="B127" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
         <v>27</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -14080,7 +14097,7 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14089,17 +14106,17 @@
     </row>
     <row r="128" spans="2:11">
       <c r="B128" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
         <v>28</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -14108,7 +14125,7 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14117,17 +14134,17 @@
     </row>
     <row r="129" spans="2:11">
       <c r="B129" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
         <v>29</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -14136,7 +14153,7 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14145,17 +14162,17 @@
     </row>
     <row r="130" spans="2:11">
       <c r="B130" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
         <v>30</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -14164,7 +14181,7 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14173,17 +14190,17 @@
     </row>
     <row r="131" spans="2:11">
       <c r="B131" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
         <v>31</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -14192,7 +14209,7 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14201,17 +14218,17 @@
     </row>
     <row r="132" spans="2:11">
       <c r="B132" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
         <v>32</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -14220,7 +14237,7 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="13"/>
@@ -14229,17 +14246,17 @@
     </row>
     <row r="133" spans="2:11">
       <c r="B133" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
         <v>99</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -14255,10 +14272,10 @@
     </row>
     <row r="134" spans="2:11">
       <c r="B134" s="6" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>1126</v>
@@ -14281,17 +14298,17 @@
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
         <v>1</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -14307,17 +14324,17 @@
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
         <v>2</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -14333,17 +14350,17 @@
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
         <v>3</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -14359,17 +14376,17 @@
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
         <v>4</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -14385,17 +14402,17 @@
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
         <v>5</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -14411,17 +14428,17 @@
     </row>
     <row r="140" spans="2:11">
       <c r="B140" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
         <v>6</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -14437,17 +14454,17 @@
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
         <v>7</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14463,17 +14480,17 @@
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
         <v>8</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -14489,17 +14506,17 @@
     </row>
     <row r="143" spans="2:11">
       <c r="B143" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
         <v>9</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -14515,17 +14532,17 @@
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
         <v>10</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -14541,17 +14558,17 @@
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
         <v>11</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -14567,17 +14584,17 @@
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
         <v>12</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -14593,17 +14610,17 @@
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
         <v>13</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -14619,17 +14636,17 @@
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
         <v>14</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -14645,17 +14662,17 @@
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
         <v>15</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -14671,17 +14688,17 @@
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
         <v>99</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -38372,13 +38389,13 @@
         <v>1291</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>1305</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18">
@@ -38389,13 +38406,13 @@
         <v>1289</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D4" s="60" t="s">
         <v>1238</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F4" s="60" t="s">
         <v>1301</v>
@@ -38407,7 +38424,7 @@
         <v>1306</v>
       </c>
       <c r="O4" s="62" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="13.2">
@@ -38444,7 +38461,7 @@
         <v>1184</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>1380</v>
@@ -38820,7 +38837,7 @@
         <v>1323</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -38834,7 +38851,7 @@
         <v>1324</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="25" spans="2:10">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C321C2C-A85A-4541-9ECF-A395726CC59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9791D985-41AA-4CAF-B252-BB13354363E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="1569">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6602,16 +6602,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>木材名CD</t>
-    <rPh sb="0" eb="2">
-      <t>モクザイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>カラー名</t>
     <rPh sb="3" eb="4">
       <t>メイ</t>
@@ -6788,6 +6778,58 @@
     <rPh sb="32" eb="33">
       <t>メイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木材名CD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ibanez</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PRS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Suhr</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MusicMan</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Zemaitis</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Momose</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.ibanez.com/jp/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.prsguitars.jp/products</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.suhr.com/suhr-custom-gallery/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.music-man.com/instruments/guitars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.zemaitis-guitars.jp/electrics/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.deviser.co.jp/momose</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10778,7 +10820,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:L150"/>
+  <dimension ref="B3:L156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -13159,7 +13201,7 @@
         <v>1431</v>
       </c>
       <c r="K93" s="5" t="str">
-        <f t="shared" ref="K93:K98" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K93:K96" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code009',1,'ESP','','',0,0.0,'https://espguitars.co.jp/products/esp');</v>
       </c>
     </row>
@@ -13220,7 +13262,7 @@
         <v>1396</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8">
@@ -13237,7 +13279,7 @@
         <v>1238</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="K96" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13266,7 +13308,7 @@
         <v>1301</v>
       </c>
       <c r="K97" s="5" t="str">
-        <f t="shared" ref="K97" si="12">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B97&amp;"'"&amp;","&amp;E97&amp;","&amp;"'"&amp;C97&amp;"'"&amp;","&amp;"'"&amp;D97&amp;"'"&amp;","&amp;"'"&amp;F97&amp;"'"&amp;","&amp;G97&amp;","&amp;H97&amp;","&amp;"'"&amp;I97&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K97:K99" si="12">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B97&amp;"'"&amp;","&amp;E97&amp;","&amp;"'"&amp;C97&amp;"'"&amp;","&amp;"'"&amp;D97&amp;"'"&amp;","&amp;"'"&amp;F97&amp;"'"&amp;","&amp;G97&amp;","&amp;H97&amp;","&amp;"'"&amp;I97&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code009',5,'SCHECTER','','',0,0.0,'https://schecter.co.jp/guitar/');</v>
       </c>
     </row>
@@ -13275,7 +13317,7 @@
         <v>1396</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8">
@@ -13289,79 +13331,77 @@
         <v>125</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="K98" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>INSERT INTO m_code VALUES ('code009',6,'ESP signature','','',0,0.0,'https://espguitars.co.jp/signatureseries/');</v>
       </c>
     </row>
     <row r="99" spans="2:11">
-      <c r="B99" s="6" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>1399</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>133</v>
+      <c r="B99" s="8" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8">
+        <v>7</v>
+      </c>
+      <c r="F99" s="8"/>
+      <c r="G99" s="9">
+        <v>0</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>1563</v>
+      </c>
+      <c r="K99" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>INSERT INTO m_code VALUES ('code009',7,'Ibanez','','',0,0.0,'https://www.ibanez.com/jp/');</v>
       </c>
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1428</v>
+        <v>1396</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1436</v>
+        <v>1558</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8">
-        <v>0</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>1435</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F100" s="8"/>
       <c r="G100" s="9">
         <v>0</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I100" s="8"/>
+      <c r="I100" s="8" t="s">
+        <v>1564</v>
+      </c>
       <c r="K100" s="5" t="str">
-        <f t="shared" ref="K100:K132" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B100&amp;"'"&amp;","&amp;E100&amp;","&amp;"'"&amp;C100&amp;"'"&amp;","&amp;"'"&amp;D100&amp;"'"&amp;","&amp;"'"&amp;F100&amp;"'"&amp;","&amp;G100&amp;","&amp;H100&amp;","&amp;"'"&amp;I100&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
+        <f t="shared" ref="K100:K101" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B100&amp;"'"&amp;","&amp;E100&amp;","&amp;"'"&amp;C100&amp;"'"&amp;","&amp;"'"&amp;D100&amp;"'"&amp;","&amp;"'"&amp;F100&amp;"'"&amp;","&amp;G100&amp;","&amp;H100&amp;","&amp;"'"&amp;I100&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code009',8,'PRS','','',0,0.0,'https://www.prsguitars.jp/products');</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1428</v>
+        <v>1396</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1437</v>
+        <v>1559</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8">
-        <v>1</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>1451</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F101" s="8"/>
       <c r="G101" s="9">
         <v>0</v>
       </c>
@@ -13369,27 +13409,25 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1475</v>
+        <v>1565</v>
       </c>
       <c r="K101" s="5" t="str">
         <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
+        <v>INSERT INTO m_code VALUES ('code009',9,'Suhr','','',0,0.0,'https://www.suhr.com/suhr-custom-gallery/');</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1428</v>
+        <v>1396</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1438</v>
+        <v>1560</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8">
-        <v>2</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>1452</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F102" s="8"/>
       <c r="G102" s="9">
         <v>0</v>
       </c>
@@ -13397,27 +13435,25 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1476</v>
+        <v>1566</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K102:K104" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code009',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1428</v>
+        <v>1396</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1439</v>
+        <v>1561</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
-        <v>3</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>1453</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F103" s="8"/>
       <c r="G103" s="9">
         <v>0</v>
       </c>
@@ -13425,27 +13461,25 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1477</v>
+        <v>1567</v>
       </c>
       <c r="K103" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <f t="shared" si="14"/>
+        <v>INSERT INTO m_code VALUES ('code009',11,'Zemaitis','','',0,0.0,'https://www.zemaitis-guitars.jp/electrics/');</v>
       </c>
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1428</v>
+        <v>1396</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1440</v>
+        <v>1562</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
-        <v>4</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>1454</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F104" s="8"/>
       <c r="G104" s="9">
         <v>0</v>
       </c>
@@ -13453,39 +13487,37 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1478</v>
+        <v>1568</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <f t="shared" si="14"/>
+        <v>INSERT INTO m_code VALUES ('code009',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
     <row r="105" spans="2:11">
-      <c r="B105" s="8" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8">
-        <v>5</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>1455</v>
-      </c>
-      <c r="G105" s="9">
-        <v>0</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>1479</v>
-      </c>
-      <c r="K105" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+      <c r="B105" s="6" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="2:11">
@@ -13493,14 +13525,14 @@
         <v>1428</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1400</v>
+        <v>1436</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1450</v>
+        <v>1435</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
@@ -13508,12 +13540,10 @@
       <c r="H106" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="8" t="s">
-        <v>1474</v>
-      </c>
+      <c r="I106" s="8"/>
       <c r="K106" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <f t="shared" ref="K106:K138" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
     <row r="107" spans="2:11">
@@ -13521,14 +13551,14 @@
         <v>1428</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -13537,11 +13567,11 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="108" spans="2:11">
@@ -13549,14 +13579,14 @@
         <v>1428</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1401</v>
+        <v>1438</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1419</v>
+        <v>1452</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -13565,11 +13595,11 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -13577,14 +13607,14 @@
         <v>1428</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -13593,11 +13623,11 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -13605,14 +13635,14 @@
         <v>1428</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1408</v>
+        <v>1440</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -13621,11 +13651,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -13633,14 +13663,14 @@
         <v>1428</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -13649,11 +13679,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -13661,14 +13691,14 @@
         <v>1428</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1420</v>
+        <v>1450</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -13677,11 +13707,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1485</v>
+        <v>1474</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -13689,14 +13719,14 @@
         <v>1428</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1403</v>
+        <v>1442</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -13705,11 +13735,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -13717,14 +13747,14 @@
         <v>1428</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1461</v>
+        <v>1419</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -13733,11 +13763,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -13745,14 +13775,14 @@
         <v>1428</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -13761,11 +13791,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -13773,14 +13803,14 @@
         <v>1428</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -13789,11 +13819,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -13801,14 +13831,14 @@
         <v>1428</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1410</v>
+        <v>1444</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -13817,11 +13847,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -13829,14 +13859,14 @@
         <v>1428</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1445</v>
+        <v>1402</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1466</v>
+        <v>1420</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -13845,11 +13875,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -13857,14 +13887,14 @@
         <v>1428</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1446</v>
+        <v>1403</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -13873,11 +13903,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -13885,14 +13915,14 @@
         <v>1428</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -13901,11 +13931,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -13913,14 +13943,14 @@
         <v>1428</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1447</v>
+        <v>1413</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1421</v>
+        <v>1462</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -13929,11 +13959,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -13941,14 +13971,14 @@
         <v>1428</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1422</v>
+        <v>1463</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -13957,11 +13987,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -13969,14 +13999,14 @@
         <v>1428</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -13985,11 +14015,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -13997,14 +14027,14 @@
         <v>1428</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1407</v>
+        <v>1445</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -14013,11 +14043,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1427</v>
+        <v>1492</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -14025,14 +14055,14 @@
         <v>1428</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -14041,11 +14071,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -14053,14 +14083,14 @@
         <v>1428</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -14069,11 +14099,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -14081,14 +14111,14 @@
         <v>1428</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1414</v>
+        <v>1447</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1472</v>
+        <v>1421</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -14097,11 +14127,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -14109,14 +14139,14 @@
         <v>1428</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -14125,11 +14155,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -14137,14 +14167,14 @@
         <v>1428</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1424</v>
+        <v>1468</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -14153,11 +14183,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -14165,14 +14195,14 @@
         <v>1428</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1417</v>
+        <v>1407</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1425</v>
+        <v>1469</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -14181,11 +14211,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1502</v>
+        <v>1427</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -14193,14 +14223,14 @@
         <v>1428</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1418</v>
+        <v>1448</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1426</v>
+        <v>1470</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -14209,11 +14239,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -14221,14 +14251,14 @@
         <v>1428</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1449</v>
+        <v>1412</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -14237,11 +14267,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>INSERT INTO m_code VALUES ('code010',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -14249,14 +14279,14 @@
         <v>1428</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1505</v>
+        <v>1414</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1505</v>
+        <v>1472</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -14264,51 +14294,55 @@
       <c r="H133" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I133" s="8"/>
+      <c r="I133" s="8" t="s">
+        <v>1499</v>
+      </c>
       <c r="K133" s="5" t="str">
-        <f t="shared" ref="K133:K150" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B133&amp;"'"&amp;","&amp;E133&amp;","&amp;"'"&amp;C133&amp;"'"&amp;","&amp;"'"&amp;D133&amp;"'"&amp;","&amp;"'"&amp;F133&amp;"'"&amp;","&amp;G133&amp;","&amp;H133&amp;","&amp;"'"&amp;I133&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
-      <c r="B134" s="6" t="s">
-        <v>1517</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>133</v>
+      <c r="B134" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D134" s="8"/>
+      <c r="E134" s="8">
+        <v>28</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G134" s="9">
+        <v>0</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K134" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="8" t="s">
-        <v>1534</v>
+        <v>1428</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1518</v>
+        <v>1416</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1535</v>
+        <v>1424</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -14316,25 +14350,27 @@
       <c r="H135" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I135" s="8"/>
+      <c r="I135" s="8" t="s">
+        <v>1501</v>
+      </c>
       <c r="K135" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="8" t="s">
-        <v>1534</v>
+        <v>1428</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1532</v>
+        <v>1417</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1536</v>
+        <v>1425</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -14342,25 +14378,27 @@
       <c r="H136" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I136" s="8"/>
+      <c r="I136" s="8" t="s">
+        <v>1502</v>
+      </c>
       <c r="K136" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="8" t="s">
-        <v>1534</v>
+        <v>1428</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1519</v>
+        <v>1418</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1537</v>
+        <v>1426</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -14368,25 +14406,27 @@
       <c r="H137" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I137" s="8"/>
+      <c r="I137" s="8" t="s">
+        <v>1503</v>
+      </c>
       <c r="K137" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="8" t="s">
-        <v>1534</v>
+        <v>1428</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1520</v>
+        <v>1449</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1538</v>
+        <v>1473</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -14394,25 +14434,27 @@
       <c r="H138" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I138" s="8"/>
+      <c r="I138" s="8" t="s">
+        <v>1504</v>
+      </c>
       <c r="K138" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="8" t="s">
-        <v>1534</v>
+        <v>1428</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1521</v>
+        <v>1505</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1539</v>
+        <v>1505</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -14422,49 +14464,49 @@
       </c>
       <c r="I139" s="8"/>
       <c r="K139" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
+        <f t="shared" ref="K139:K156" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
-      <c r="B140" s="8" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>1522</v>
-      </c>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8">
-        <v>6</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>1540</v>
-      </c>
-      <c r="G140" s="9">
-        <v>0</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I140" s="8"/>
-      <c r="K140" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+      <c r="B140" s="6" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14474,23 +14516,23 @@
       </c>
       <c r="I141" s="8"/>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -14500,23 +14542,23 @@
       </c>
       <c r="I142" s="8"/>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
       <c r="B143" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -14526,23 +14568,23 @@
       </c>
       <c r="I143" s="8"/>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -14552,23 +14594,23 @@
       </c>
       <c r="I144" s="8"/>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -14578,23 +14620,23 @@
       </c>
       <c r="I145" s="8"/>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -14604,23 +14646,23 @@
       </c>
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1533</v>
+        <v>1522</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -14630,23 +14672,23 @@
       </c>
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -14656,23 +14698,23 @@
       </c>
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -14682,23 +14724,23 @@
       </c>
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -14708,7 +14750,163 @@
       </c>
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="151" spans="2:11">
+      <c r="B151" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8">
+        <v>11</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G151" s="9">
+        <v>0</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I151" s="8"/>
+      <c r="K151" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11">
+      <c r="B152" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8">
+        <v>12</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G152" s="9">
+        <v>0</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I152" s="8"/>
+      <c r="K152" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11">
+      <c r="B153" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D153" s="8"/>
+      <c r="E153" s="8">
+        <v>13</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G153" s="9">
+        <v>0</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I153" s="8"/>
+      <c r="K153" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11">
+      <c r="B154" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D154" s="8"/>
+      <c r="E154" s="8">
+        <v>14</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G154" s="9">
+        <v>0</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I154" s="8"/>
+      <c r="K154" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="155" spans="2:11">
+      <c r="B155" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8">
+        <v>15</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G155" s="9">
+        <v>0</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I155" s="8"/>
+      <c r="K155" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11">
+      <c r="B156" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8">
+        <v>99</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G156" s="9">
+        <v>0</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I156" s="8"/>
+      <c r="K156" s="5" t="str">
+        <f t="shared" si="16"/>
         <v>INSERT INTO m_code VALUES ('code011',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
@@ -18266,7 +18464,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -18299,7 +18497,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -18332,7 +18530,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -18362,7 +18560,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -18395,7 +18593,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -18425,7 +18623,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -18458,7 +18656,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -18488,7 +18686,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -18521,7 +18719,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -18554,7 +18752,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -18584,7 +18782,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -18617,7 +18815,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -18650,7 +18848,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -18680,7 +18878,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -18713,7 +18911,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -18743,7 +18941,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -18776,7 +18974,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -18809,7 +19007,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -18839,7 +19037,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -18872,7 +19070,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -18905,7 +19103,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -18935,7 +19133,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -18968,7 +19166,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -18998,7 +19196,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -19031,7 +19229,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -19061,7 +19259,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -19094,7 +19292,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -19127,7 +19325,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -19160,7 +19358,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -19190,7 +19388,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -19223,7 +19421,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -19256,7 +19454,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -19286,7 +19484,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -19319,7 +19517,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -19352,7 +19550,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -19383,7 +19581,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -19416,7 +19614,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -19449,7 +19647,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -19482,7 +19680,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -19512,7 +19710,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -19545,7 +19743,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -19578,7 +19776,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -19608,7 +19806,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -19641,7 +19839,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -19674,7 +19872,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -19704,7 +19902,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -19737,7 +19935,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -19770,7 +19968,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -19800,7 +19998,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -19830,7 +20028,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -19860,7 +20058,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -19890,7 +20088,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -19920,7 +20118,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -19953,7 +20151,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -19986,7 +20184,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -20016,7 +20214,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -20046,7 +20244,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -20076,7 +20274,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -20109,7 +20307,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -20142,7 +20340,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -20172,7 +20370,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -20205,7 +20403,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -20238,7 +20436,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -20271,7 +20469,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -20301,7 +20499,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -20331,7 +20529,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -20361,7 +20559,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -20391,7 +20589,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -20421,7 +20619,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -20451,7 +20649,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -20481,7 +20679,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -20511,7 +20709,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -20541,7 +20739,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -20571,7 +20769,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -20601,7 +20799,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -20631,7 +20829,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -20661,7 +20859,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -20693,7 +20891,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -20725,7 +20923,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -20755,7 +20953,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -20788,7 +20986,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -20821,7 +21019,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -20851,7 +21049,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -20881,7 +21079,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>
@@ -38395,7 +38593,7 @@
         <v>1305</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18">
@@ -38406,7 +38604,7 @@
         <v>1289</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D4" s="60" t="s">
         <v>1238</v>
@@ -38424,7 +38622,7 @@
         <v>1306</v>
       </c>
       <c r="O4" s="62" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="13.2">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9791D985-41AA-4CAF-B252-BB13354363E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD68BB7-CA07-4F9B-8DA7-A31D767FCFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -5834,9 +5834,6 @@
     <t>string_spacing_at_bridge_imperial</t>
   </si>
   <si>
-    <t>https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB</t>
-  </si>
-  <si>
     <t>https://espguitars.co.jp/products/esp</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6830,6 +6827,10 @@
   </si>
   <si>
     <t>https://www.deviser.co.jp/momose</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://gibson.jp/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10841,7 +10842,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="6" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1153</v>
@@ -11049,7 +11050,7 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="6" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1154</v>
@@ -11365,7 +11366,7 @@
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="6" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1155</v>
@@ -11625,7 +11626,7 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="6" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>1156</v>
@@ -11903,7 +11904,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="6" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>1157</v>
@@ -12007,7 +12008,7 @@
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="6" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>1158</v>
@@ -12849,7 +12850,7 @@
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="6" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>1159</v>
@@ -13057,7 +13058,7 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="6" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>1160</v>
@@ -13155,10 +13156,10 @@
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="6" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>1126</v>
@@ -13181,7 +13182,7 @@
     </row>
     <row r="93" spans="2:11">
       <c r="B93" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>1183</v>
@@ -13198,7 +13199,7 @@
         <v>125</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="K93" s="5" t="str">
         <f t="shared" ref="K93:K96" si="11">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B93&amp;"'"&amp;","&amp;E93&amp;","&amp;"'"&amp;C93&amp;"'"&amp;","&amp;"'"&amp;D93&amp;"'"&amp;","&amp;"'"&amp;F93&amp;"'"&amp;","&amp;G93&amp;","&amp;H93&amp;","&amp;"'"&amp;I93&amp;"'"&amp;");"</f>
@@ -13207,10 +13208,10 @@
     </row>
     <row r="94" spans="2:11">
       <c r="B94" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8">
@@ -13224,7 +13225,7 @@
         <v>125</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="K94" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13233,7 +13234,7 @@
     </row>
     <row r="95" spans="2:11">
       <c r="B95" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>1197</v>
@@ -13250,19 +13251,19 @@
         <v>125</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>1288</v>
+        <v>1568</v>
       </c>
       <c r="K95" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>INSERT INTO m_code VALUES ('code009',3,'Gibson','','',0,0.0,'https://gibson.jp/?utm_source=google&amp;utm_medium=search&amp;utm_campaign=gibson&amp;gad_source=1&amp;gad_campaignid=17283607633&amp;gbraid=0AAAAAoTX0VKp4CAYqmVLrRV8_llB-MDuY&amp;gclid=Cj0KCQjwz9_QBhD_ARIsADnSCfAwPwvBwnhTpCNjOaBHtHQQSA99HkobitjcY6mrV9aCelM8Qn3gIKAaAizSEALw_wcB');</v>
+        <v>INSERT INTO m_code VALUES ('code009',3,'Gibson','','',0,0.0,'https://gibson.jp/');</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="B96" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8">
@@ -13279,7 +13280,7 @@
         <v>1238</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="K96" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13288,10 +13289,10 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8">
@@ -13305,7 +13306,7 @@
         <v>125</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="K97" s="5" t="str">
         <f t="shared" ref="K97:K99" si="12">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B97&amp;"'"&amp;","&amp;E97&amp;","&amp;"'"&amp;C97&amp;"'"&amp;","&amp;"'"&amp;D97&amp;"'"&amp;","&amp;"'"&amp;F97&amp;"'"&amp;","&amp;G97&amp;","&amp;H97&amp;","&amp;"'"&amp;I97&amp;"'"&amp;");"</f>
@@ -13314,10 +13315,10 @@
     </row>
     <row r="98" spans="2:11">
       <c r="B98" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8">
@@ -13331,7 +13332,7 @@
         <v>125</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="K98" s="5" t="str">
         <f t="shared" si="12"/>
@@ -13340,10 +13341,10 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8">
@@ -13357,7 +13358,7 @@
         <v>125</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K99" s="5" t="str">
         <f t="shared" si="12"/>
@@ -13366,10 +13367,10 @@
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8">
@@ -13383,7 +13384,7 @@
         <v>125</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K100" s="5" t="str">
         <f t="shared" ref="K100:K101" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B100&amp;"'"&amp;","&amp;E100&amp;","&amp;"'"&amp;C100&amp;"'"&amp;","&amp;"'"&amp;D100&amp;"'"&amp;","&amp;"'"&amp;F100&amp;"'"&amp;","&amp;G100&amp;","&amp;H100&amp;","&amp;"'"&amp;I100&amp;"'"&amp;");"</f>
@@ -13392,10 +13393,10 @@
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8">
@@ -13409,7 +13410,7 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K101" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13418,10 +13419,10 @@
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8">
@@ -13435,7 +13436,7 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K102" s="5" t="str">
         <f t="shared" ref="K102:K104" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
@@ -13444,10 +13445,10 @@
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
@@ -13461,7 +13462,7 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K103" s="5" t="str">
         <f t="shared" si="14"/>
@@ -13470,10 +13471,10 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
@@ -13487,7 +13488,7 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="K104" s="5" t="str">
         <f t="shared" si="14"/>
@@ -13496,10 +13497,10 @@
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="6" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>1126</v>
@@ -13522,17 +13523,17 @@
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
         <v>0</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
@@ -13548,17 +13549,17 @@
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
         <v>1</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -13567,7 +13568,7 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K107" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13576,17 +13577,17 @@
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
         <v>2</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -13595,7 +13596,7 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K108" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13604,17 +13605,17 @@
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
         <v>3</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -13623,7 +13624,7 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K109" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13632,17 +13633,17 @@
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
         <v>4</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -13651,7 +13652,7 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K110" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13660,17 +13661,17 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
         <v>5</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -13679,7 +13680,7 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13688,17 +13689,17 @@
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
         <v>6</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -13707,7 +13708,7 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13716,17 +13717,17 @@
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
         <v>7</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -13735,7 +13736,7 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13744,17 +13745,17 @@
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
         <v>8</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -13763,7 +13764,7 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13772,17 +13773,17 @@
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
         <v>9</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -13791,7 +13792,7 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13800,17 +13801,17 @@
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
         <v>10</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -13819,7 +13820,7 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13828,17 +13829,17 @@
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
         <v>11</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -13847,7 +13848,7 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13856,17 +13857,17 @@
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
         <v>12</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -13875,7 +13876,7 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13884,17 +13885,17 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
         <v>13</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -13903,7 +13904,7 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13912,17 +13913,17 @@
     </row>
     <row r="120" spans="2:11">
       <c r="B120" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
         <v>14</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -13931,7 +13932,7 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13940,17 +13941,17 @@
     </row>
     <row r="121" spans="2:11">
       <c r="B121" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
         <v>15</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -13959,7 +13960,7 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13968,17 +13969,17 @@
     </row>
     <row r="122" spans="2:11">
       <c r="B122" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
         <v>16</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -13987,7 +13988,7 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="15"/>
@@ -13996,17 +13997,17 @@
     </row>
     <row r="123" spans="2:11">
       <c r="B123" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
         <v>17</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -14015,7 +14016,7 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14024,17 +14025,17 @@
     </row>
     <row r="124" spans="2:11">
       <c r="B124" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
         <v>18</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -14043,7 +14044,7 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14052,17 +14053,17 @@
     </row>
     <row r="125" spans="2:11">
       <c r="B125" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
         <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -14071,7 +14072,7 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14080,17 +14081,17 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
         <v>20</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -14099,7 +14100,7 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14108,17 +14109,17 @@
     </row>
     <row r="127" spans="2:11">
       <c r="B127" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
         <v>21</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -14127,7 +14128,7 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14136,17 +14137,17 @@
     </row>
     <row r="128" spans="2:11">
       <c r="B128" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
         <v>22</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -14155,7 +14156,7 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14164,17 +14165,17 @@
     </row>
     <row r="129" spans="2:11">
       <c r="B129" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
         <v>23</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -14183,7 +14184,7 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14192,17 +14193,17 @@
     </row>
     <row r="130" spans="2:11">
       <c r="B130" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
         <v>24</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -14211,7 +14212,7 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14220,17 +14221,17 @@
     </row>
     <row r="131" spans="2:11">
       <c r="B131" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
         <v>25</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -14239,7 +14240,7 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14248,17 +14249,17 @@
     </row>
     <row r="132" spans="2:11">
       <c r="B132" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
         <v>26</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -14267,7 +14268,7 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14276,17 +14277,17 @@
     </row>
     <row r="133" spans="2:11">
       <c r="B133" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
         <v>27</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -14295,7 +14296,7 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14304,17 +14305,17 @@
     </row>
     <row r="134" spans="2:11">
       <c r="B134" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
         <v>28</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -14323,7 +14324,7 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14332,17 +14333,17 @@
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
         <v>29</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -14351,7 +14352,7 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14360,17 +14361,17 @@
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
         <v>30</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -14379,7 +14380,7 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14388,17 +14389,17 @@
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
         <v>31</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -14407,7 +14408,7 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14416,17 +14417,17 @@
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
         <v>32</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -14435,7 +14436,7 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14444,17 +14445,17 @@
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
         <v>99</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -14470,10 +14471,10 @@
     </row>
     <row r="140" spans="2:11">
       <c r="B140" s="6" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>1126</v>
@@ -14496,17 +14497,17 @@
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
         <v>1</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14522,17 +14523,17 @@
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
         <v>2</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -14548,17 +14549,17 @@
     </row>
     <row r="143" spans="2:11">
       <c r="B143" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
         <v>3</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -14574,17 +14575,17 @@
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
         <v>4</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -14600,17 +14601,17 @@
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
         <v>5</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -14626,17 +14627,17 @@
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
         <v>6</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -14652,17 +14653,17 @@
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
         <v>7</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -14678,17 +14679,17 @@
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
         <v>8</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -14704,17 +14705,17 @@
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
         <v>9</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -14730,17 +14731,17 @@
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
         <v>10</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -14756,17 +14757,17 @@
     </row>
     <row r="151" spans="2:11">
       <c r="B151" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
         <v>11</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -14782,17 +14783,17 @@
     </row>
     <row r="152" spans="2:11">
       <c r="B152" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
         <v>12</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -14808,17 +14809,17 @@
     </row>
     <row r="153" spans="2:11">
       <c r="B153" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
         <v>13</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -14834,17 +14835,17 @@
     </row>
     <row r="154" spans="2:11">
       <c r="B154" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
         <v>14</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -14860,17 +14861,17 @@
     </row>
     <row r="155" spans="2:11">
       <c r="B155" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
         <v>15</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -14886,17 +14887,17 @@
     </row>
     <row r="156" spans="2:11">
       <c r="B156" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
         <v>99</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -38584,45 +38585,45 @@
         <v>1236</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18">
       <c r="A4" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D4" s="60" t="s">
         <v>1238</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="O4" s="62" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="13.2">
@@ -38636,10 +38637,10 @@
         <v>1239</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="13.2">
@@ -38653,16 +38654,16 @@
         <v>1240</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>1184</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="13.2">
@@ -38676,19 +38677,19 @@
         <v>1241</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>1185</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="13.2">
@@ -38705,16 +38706,16 @@
         <v>1208</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="13.2">
@@ -38734,7 +38735,7 @@
         <v>1212</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>1206</v>
@@ -38757,13 +38758,13 @@
         <v>1188</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>1203</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="13.2">
@@ -38777,19 +38778,19 @@
         <v>1195</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>1217</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>1194</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="13.2">
@@ -38809,13 +38810,13 @@
         <v>1195</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="13.2">
@@ -38835,7 +38836,7 @@
         <v>1194</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>1196</v>
@@ -38855,13 +38856,13 @@
         <v>1213</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="13.2">
@@ -38878,13 +38879,13 @@
         <v>1214</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="13.2">
@@ -38898,13 +38899,13 @@
         <v>1249</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="13.2">
@@ -38918,10 +38919,10 @@
         <v>1202</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>1216</v>
@@ -38938,13 +38939,13 @@
         <v>1203</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="13.2">
@@ -38961,7 +38962,7 @@
         <v>1194</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>1253</v>
@@ -38981,10 +38982,10 @@
         <v>1224</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -38998,10 +38999,10 @@
         <v>1273</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -39012,10 +39013,10 @@
         <v>1253</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>1208</v>
@@ -39032,10 +39033,10 @@
         <v>1220</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -39046,10 +39047,10 @@
         <v>1255</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -39060,10 +39061,10 @@
         <v>1208</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="26" spans="2:10">
@@ -39074,7 +39075,7 @@
         <v>1256</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="27" spans="2:10">
@@ -39085,7 +39086,7 @@
         <v>1257</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="28" spans="2:10">
@@ -39096,7 +39097,7 @@
         <v>1258</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="29" spans="2:10">
@@ -39107,7 +39108,7 @@
         <v>1226</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="30" spans="2:10">
@@ -39118,7 +39119,7 @@
         <v>1259</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="31" spans="2:10">
@@ -39129,7 +39130,7 @@
         <v>1225</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="32" spans="2:10">
@@ -39140,7 +39141,7 @@
         <v>1260</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="33" spans="3:8">
@@ -39151,7 +39152,7 @@
         <v>1261</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="34" spans="3:8">
@@ -39162,7 +39163,7 @@
         <v>1262</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="35" spans="3:8">
@@ -39173,7 +39174,7 @@
         <v>1263</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="36" spans="3:8">
@@ -39184,7 +39185,7 @@
         <v>1264</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="37" spans="3:8">
@@ -39195,7 +39196,7 @@
         <v>1265</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="38" spans="3:8">
@@ -39206,7 +39207,7 @@
         <v>1266</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="39" spans="3:8">
@@ -39217,7 +39218,7 @@
         <v>1267</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="40" spans="3:8">
@@ -39228,7 +39229,7 @@
         <v>1268</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="41" spans="3:8">
@@ -39239,7 +39240,7 @@
         <v>1269</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="42" spans="3:8">
@@ -39247,7 +39248,7 @@
         <v>1270</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="43" spans="3:8">
@@ -39255,7 +39256,7 @@
         <v>1271</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="44" spans="3:8">
@@ -39263,7 +39264,7 @@
         <v>1272</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="45" spans="3:8">
@@ -39271,7 +39272,7 @@
         <v>1189</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="46" spans="3:8">
@@ -39279,7 +39280,7 @@
         <v>1273</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="47" spans="3:8">
@@ -39287,7 +39288,7 @@
         <v>1194</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="48" spans="3:8">
@@ -39295,7 +39296,7 @@
         <v>1274</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="49" spans="4:8">
@@ -39303,7 +39304,7 @@
         <v>1275</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="50" spans="4:8">
@@ -39311,7 +39312,7 @@
         <v>1221</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="51" spans="4:8">
@@ -39319,7 +39320,7 @@
         <v>1276</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="52" spans="4:8">
@@ -39327,7 +39328,7 @@
         <v>1277</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="53" spans="4:8">
@@ -39335,7 +39336,7 @@
         <v>1278</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="54" spans="4:8">
@@ -39343,7 +39344,7 @@
         <v>1279</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="55" spans="4:8">
@@ -39351,7 +39352,7 @@
         <v>1280</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="56" spans="4:8">
@@ -39359,7 +39360,7 @@
         <v>1281</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="57" spans="4:8">
@@ -39367,7 +39368,7 @@
         <v>1282</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="58" spans="4:8">
@@ -39375,7 +39376,7 @@
         <v>1283</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="59" spans="4:8">
@@ -39383,7 +39384,7 @@
         <v>1284</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="60" spans="4:8">
@@ -39391,7 +39392,7 @@
         <v>1285</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="61" spans="4:8">
@@ -39399,7 +39400,7 @@
         <v>1286</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="62" spans="4:8">
@@ -39407,92 +39408,92 @@
         <v>1287</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="63" spans="4:8">
       <c r="H63" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="64" spans="4:8">
       <c r="H64" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="65" spans="8:8">
       <c r="H65" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="66" spans="8:8">
       <c r="H66" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="67" spans="8:8">
       <c r="H67" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="68" spans="8:8">
       <c r="H68" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="69" spans="8:8">
       <c r="H69" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="70" spans="8:8">
       <c r="H70" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="71" spans="8:8">
       <c r="H71" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="72" spans="8:8">
       <c r="H72" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="73" spans="8:8">
       <c r="H73" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="74" spans="8:8">
       <c r="H74" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="75" spans="8:8">
       <c r="H75" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="76" spans="8:8">
       <c r="H76" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="77" spans="8:8">
       <c r="H77" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="78" spans="8:8">
       <c r="H78" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="79" spans="8:8">
       <c r="H79" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
   </sheetData>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD68BB7-CA07-4F9B-8DA7-A31D767FCFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B91CF2-28DA-4DB8-B5CC-26A3D9EDFA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3628" uniqueCount="1572">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6831,6 +6831,42 @@
   </si>
   <si>
     <t>https://gibson.jp/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メーカー並列処理</t>
+    <rPh sb="4" eb="6">
+      <t>ヘイレツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メモリ2GBだと、並列数２が限界そう</t>
+    <rPh sb="9" eb="11">
+      <t>ヘイレツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>32GBなら10並列でも全く問題なし</t>
+    <rPh sb="8" eb="10">
+      <t>ヘイレツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -38691,6 +38727,9 @@
       <c r="K7" s="1" t="s">
         <v>1389</v>
       </c>
+      <c r="O7" s="1" t="s">
+        <v>1569</v>
+      </c>
     </row>
     <row r="8" spans="1:15" ht="13.2">
       <c r="B8" s="58" t="s">
@@ -38717,6 +38756,9 @@
       <c r="K8" s="1" t="s">
         <v>1390</v>
       </c>
+      <c r="O8" s="1" t="s">
+        <v>1570</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="13.2">
       <c r="B9" s="58" t="s">
@@ -38739,6 +38781,9 @@
       </c>
       <c r="J9" s="1" t="s">
         <v>1206</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>1571</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.2">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B91CF2-28DA-4DB8-B5CC-26A3D9EDFA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336A3067-B34B-4F6A-AD63-0DF488CB6CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3628" uniqueCount="1572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="1578">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6867,6 +6867,30 @@
     <rPh sb="14" eb="16">
       <t>モンダイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Okoume</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オクメ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マホガニーに近く、中低域が豊かで軽量。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メランティ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Meranti</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>中域寄りで温かめ、マホガニー系に近い。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10857,7 +10881,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:L156"/>
+  <dimension ref="B3:L158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -13579,7 +13603,7 @@
       </c>
       <c r="I106" s="8"/>
       <c r="K106" s="5" t="str">
-        <f t="shared" ref="K106:K138" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K106:K140" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
@@ -14484,14 +14508,14 @@
         <v>1427</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1504</v>
+        <v>1572</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1504</v>
+        <v>1573</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -14499,51 +14523,55 @@
       <c r="H139" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I139" s="8"/>
+      <c r="I139" s="8" t="s">
+        <v>1574</v>
+      </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" ref="K139:K156" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
+        <f t="shared" ref="K139" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
-      <c r="B140" s="6" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>133</v>
+      <c r="B140" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8">
+        <v>34</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G140" s="9">
+        <v>0</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K140" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1532</v>
+        <v>1427</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1533</v>
+        <v>1504</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14553,34 +14581,34 @@
       </c>
       <c r="I141" s="8"/>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
+        <f t="shared" ref="K141:K158" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
-      <c r="B142" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8">
-        <v>2</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>1534</v>
-      </c>
-      <c r="G142" s="9">
-        <v>0</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I142" s="8"/>
-      <c r="K142" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
+      <c r="B142" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -14588,14 +14616,14 @@
         <v>1532</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -14605,8 +14633,8 @@
       </c>
       <c r="I143" s="8"/>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -14614,14 +14642,14 @@
         <v>1532</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1518</v>
+        <v>1530</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -14631,8 +14659,8 @@
       </c>
       <c r="I144" s="8"/>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -14640,14 +14668,14 @@
         <v>1532</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -14657,8 +14685,8 @@
       </c>
       <c r="I145" s="8"/>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -14666,14 +14694,14 @@
         <v>1532</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -14683,8 +14711,8 @@
       </c>
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -14692,14 +14720,14 @@
         <v>1532</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -14709,8 +14737,8 @@
       </c>
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -14718,14 +14746,14 @@
         <v>1532</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -14735,8 +14763,8 @@
       </c>
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -14744,14 +14772,14 @@
         <v>1532</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -14761,8 +14789,8 @@
       </c>
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -14770,14 +14798,14 @@
         <v>1532</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -14787,8 +14815,8 @@
       </c>
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -14796,14 +14824,14 @@
         <v>1532</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -14813,8 +14841,8 @@
       </c>
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -14822,14 +14850,14 @@
         <v>1532</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -14839,8 +14867,8 @@
       </c>
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -14848,14 +14876,14 @@
         <v>1532</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -14865,8 +14893,8 @@
       </c>
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -14874,14 +14902,14 @@
         <v>1532</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -14891,8 +14919,8 @@
       </c>
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -14900,14 +14928,14 @@
         <v>1532</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -14917,8 +14945,8 @@
       </c>
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -14926,14 +14954,14 @@
         <v>1532</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -14943,7 +14971,59 @@
       </c>
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="157" spans="2:11">
+      <c r="B157" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D157" s="8"/>
+      <c r="E157" s="8">
+        <v>15</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G157" s="9">
+        <v>0</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I157" s="8"/>
+      <c r="K157" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="158" spans="2:11">
+      <c r="B158" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D158" s="8"/>
+      <c r="E158" s="8">
+        <v>99</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G158" s="9">
+        <v>0</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I158" s="8"/>
+      <c r="K158" s="5" t="str">
+        <f t="shared" si="17"/>
         <v>INSERT INTO m_code VALUES ('code011',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336A3067-B34B-4F6A-AD63-0DF488CB6CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B11CB75-4F27-4C42-98B6-0350F7B034FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="1578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1584">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6891,6 +6891,30 @@
   </si>
   <si>
     <t>中域寄りで温かめ、マホガニー系に近い。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Sakura</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サクラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Tochi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>トチ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10881,7 +10905,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:L158"/>
+  <dimension ref="B3:L160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -13603,7 +13627,7 @@
       </c>
       <c r="I106" s="8"/>
       <c r="K106" s="5" t="str">
-        <f t="shared" ref="K106:K140" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K106:K142" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
@@ -14527,7 +14551,7 @@
         <v>1574</v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" ref="K139" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO m_code VALUES ('code010',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
@@ -14555,7 +14579,7 @@
         <v>1577</v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="K140" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code010',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
@@ -14564,14 +14588,14 @@
         <v>1427</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1504</v>
+        <v>1578</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1504</v>
+        <v>1579</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14579,51 +14603,55 @@
       <c r="H141" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I141" s="8"/>
+      <c r="I141" s="8" t="s">
+        <v>1583</v>
+      </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" ref="K141:K158" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
+        <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
-      <c r="B142" s="6" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>133</v>
+      <c r="B142" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8">
+        <v>36</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G142" s="9">
+        <v>0</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>1582</v>
+      </c>
+      <c r="K142" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
       <c r="B143" s="8" t="s">
-        <v>1532</v>
+        <v>1427</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1533</v>
+        <v>1504</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -14633,34 +14661,34 @@
       </c>
       <c r="I143" s="8"/>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
+        <f t="shared" ref="K143:K160" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
-      <c r="B144" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8">
-        <v>2</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>1534</v>
-      </c>
-      <c r="G144" s="9">
-        <v>0</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I144" s="8"/>
-      <c r="K144" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
+      <c r="B144" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -14668,14 +14696,14 @@
         <v>1532</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -14685,8 +14713,8 @@
       </c>
       <c r="I145" s="8"/>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -14694,14 +14722,14 @@
         <v>1532</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1518</v>
+        <v>1530</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -14711,8 +14739,8 @@
       </c>
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -14720,14 +14748,14 @@
         <v>1532</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -14737,8 +14765,8 @@
       </c>
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -14746,14 +14774,14 @@
         <v>1532</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -14763,8 +14791,8 @@
       </c>
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -14772,14 +14800,14 @@
         <v>1532</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -14789,8 +14817,8 @@
       </c>
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -14798,14 +14826,14 @@
         <v>1532</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -14815,8 +14843,8 @@
       </c>
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -14824,14 +14852,14 @@
         <v>1532</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -14841,8 +14869,8 @@
       </c>
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -14850,14 +14878,14 @@
         <v>1532</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -14867,8 +14895,8 @@
       </c>
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -14876,14 +14904,14 @@
         <v>1532</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -14893,8 +14921,8 @@
       </c>
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -14902,14 +14930,14 @@
         <v>1532</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -14919,8 +14947,8 @@
       </c>
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -14928,14 +14956,14 @@
         <v>1532</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -14945,8 +14973,8 @@
       </c>
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -14954,14 +14982,14 @@
         <v>1532</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -14971,8 +14999,8 @@
       </c>
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -14980,14 +15008,14 @@
         <v>1532</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -14997,8 +15025,8 @@
       </c>
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -15006,14 +15034,14 @@
         <v>1532</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -15023,7 +15051,59 @@
       </c>
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="159" spans="2:11">
+      <c r="B159" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D159" s="8"/>
+      <c r="E159" s="8">
+        <v>15</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G159" s="9">
+        <v>0</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I159" s="8"/>
+      <c r="K159" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11">
+      <c r="B160" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8">
+        <v>99</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G160" s="9">
+        <v>0</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I160" s="8"/>
+      <c r="K160" s="5" t="str">
+        <f t="shared" si="18"/>
         <v>INSERT INTO m_code VALUES ('code011',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B11CB75-4F27-4C42-98B6-0350F7B034FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621D786-2071-4ECD-A1F2-96C4FDD67F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -6798,10 +6798,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Zemaitis</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Momose</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6915,6 +6911,10 @@
   </si>
   <si>
     <t>中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ZEMAITIS</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13335,7 +13335,7 @@
         <v>125</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="K95" s="5" t="str">
         <f t="shared" si="11"/>
@@ -13442,7 +13442,7 @@
         <v>125</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K99" s="5" t="str">
         <f t="shared" si="12"/>
@@ -13468,7 +13468,7 @@
         <v>125</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K100" s="5" t="str">
         <f t="shared" ref="K100:K101" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B100&amp;"'"&amp;","&amp;E100&amp;","&amp;"'"&amp;C100&amp;"'"&amp;","&amp;"'"&amp;D100&amp;"'"&amp;","&amp;"'"&amp;F100&amp;"'"&amp;","&amp;G100&amp;","&amp;H100&amp;","&amp;"'"&amp;I100&amp;"'"&amp;");"</f>
@@ -13494,7 +13494,7 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K101" s="5" t="str">
         <f t="shared" si="13"/>
@@ -13520,7 +13520,7 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K102" s="5" t="str">
         <f t="shared" ref="K102:K104" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
@@ -13532,7 +13532,7 @@
         <v>1395</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1560</v>
+        <v>1583</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
@@ -13546,11 +13546,11 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K103" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('code009',11,'Zemaitis','','',0,0.0,'https://www.zemaitis-guitars.jp/electrics/');</v>
+        <v>INSERT INTO m_code VALUES ('code009',11,'ZEMAITIS','','',0,0.0,'https://www.zemaitis-guitars.jp/electrics/');</v>
       </c>
     </row>
     <row r="104" spans="2:11">
@@ -13558,7 +13558,7 @@
         <v>1395</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
@@ -13572,7 +13572,7 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K104" s="5" t="str">
         <f t="shared" si="14"/>
@@ -14532,14 +14532,14 @@
         <v>1427</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
         <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="15"/>
@@ -14560,14 +14560,14 @@
         <v>1427</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
         <v>34</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -14576,7 +14576,7 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" ref="K140" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
@@ -14588,14 +14588,14 @@
         <v>1427</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
         <v>35</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -14604,7 +14604,7 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
@@ -14616,14 +14616,14 @@
         <v>1427</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
         <v>36</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -14632,7 +14632,7 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K142" s="5" t="str">
         <f t="shared" si="15"/>
@@ -38888,7 +38888,7 @@
         <v>1389</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="13.2">
@@ -38917,7 +38917,7 @@
         <v>1390</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="13.2">
@@ -38943,7 +38943,7 @@
         <v>1206</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.2">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621D786-2071-4ECD-A1F2-96C4FDD67F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B86953F-68C7-4A29-8F09-66E2D324A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="戦績レポート" sheetId="7" r:id="rId7"/>
     <sheet name="各種設定" sheetId="8" r:id="rId8"/>
     <sheet name="guitarCrawler" sheetId="9" r:id="rId9"/>
+    <sheet name="public API" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="1680">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6916,6 +6917,342 @@
   <si>
     <t>ZEMAITIS</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メーカー [ Fender ▼ ]</t>
+  </si>
+  <si>
+    <t>シリーズ [ Stratocaster ▼ ]</t>
+  </si>
+  <si>
+    <t>カラー [ Blue ▼ ]</t>
+  </si>
+  <si>
+    <t>価格 [100000] ～ [300000]</t>
+  </si>
+  <si>
+    <t>ボディ材 [ Mahogany ▼ ]</t>
+  </si>
+  <si>
+    <t>&amp;series=Stratocaster</t>
+  </si>
+  <si>
+    <t>&amp;color=Blue</t>
+  </si>
+  <si>
+    <t>&amp;bodyMaterial=Mahogany</t>
+  </si>
+  <si>
+    <t>&amp;name=player</t>
+  </si>
+  <si>
+    <t>&amp;minPrice=100000</t>
+  </si>
+  <si>
+    <t>&amp;maxPrice=300000</t>
+  </si>
+  <si>
+    <t>&amp;page=1</t>
+  </si>
+  <si>
+    <t>&amp;pageSize=20</t>
+  </si>
+  <si>
+    <t>?maker=Fender</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>昇順 or 降順</t>
+    <rPh sb="0" eb="2">
+      <t>ショウジュン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウジュン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>画面検索部イメージ</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/series</t>
+  </si>
+  <si>
+    <t>GET /api/colors</t>
+  </si>
+  <si>
+    <t>GET /api/body-materials</t>
+  </si>
+  <si>
+    <t>&lt;select&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;option&gt;Fender&lt;/option&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;option&gt;PRS&lt;/option&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;option&gt;Ibanez&lt;/option&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/select&gt;</t>
+  </si>
+  <si>
+    <t>画面側でのハードコーディングが不要。</t>
+    <rPh sb="15" eb="17">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レスポンスイメージ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t>"id": 123,</t>
+  </si>
+  <si>
+    <t>"name": "...",</t>
+  </si>
+  <si>
+    <t>"manufacturer": "...",</t>
+  </si>
+  <si>
+    <t>"bodyMaterial": "...",</t>
+  </si>
+  <si>
+    <t>"price": ...</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>”…": ….</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"totalCount": 4300,</t>
+  </si>
+  <si>
+    <t>"page": 1,</t>
+  </si>
+  <si>
+    <t>manufacturer</t>
+  </si>
+  <si>
+    <t>bodyMaterial</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>minPrice</t>
+  </si>
+  <si>
+    <t>maxPrice</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>pageSize</t>
+  </si>
+  <si>
+    <t>sort</t>
+  </si>
+  <si>
+    <t>お遊びAPI</t>
+  </si>
+  <si>
+    <t>GET /api/guitars/random</t>
+  </si>
+  <si>
+    <t>一般的なページング</t>
+  </si>
+  <si>
+    <t>フロント</t>
+  </si>
+  <si>
+    <t>GET /api/guitars?page=1&amp;pageSize=20</t>
+  </si>
+  <si>
+    <t>2ページ目なら</t>
+  </si>
+  <si>
+    <t>GET /api/guitars?page=2&amp;pageSize=20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "totalCount": 4321,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "pageSize": 20</t>
+  </si>
+  <si>
+    <t>なら</t>
+  </si>
+  <si>
+    <t>4321 ÷ 20</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>217ページ</t>
+  </si>
+  <si>
+    <t>と計算できる。</t>
+  </si>
+  <si>
+    <t>Query(必要そうなparams)</t>
+    <rPh sb="6" eb="8">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public class GuitarSearchRequest</t>
+  </si>
+  <si>
+    <t>public string? Manufacturer { get; set; }</t>
+  </si>
+  <si>
+    <t>public string? Series { get; set; }</t>
+  </si>
+  <si>
+    <t>public string? Color { get; set; }</t>
+  </si>
+  <si>
+    <t>public string? BodyMaterial { get; set; }</t>
+  </si>
+  <si>
+    <t>public int? MinPrice { get; set; }</t>
+  </si>
+  <si>
+    <t>public int? MaxPrice { get; set; }</t>
+  </si>
+  <si>
+    <t>public string? Sort { get; set; }</t>
+  </si>
+  <si>
+    <t>public int Page { get; set; } = 1;</t>
+  </si>
+  <si>
+    <t>public int PageSize { get; set; } = 20;</t>
+  </si>
+  <si>
+    <t>DTO案</t>
+    <rPh sb="3" eb="4">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>補助API(マスタ検索)</t>
+    <rPh sb="0" eb="2">
+      <t>ホジョ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/manufacturers</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SELECT *</t>
+  </si>
+  <si>
+    <t>FROM guitars</t>
+  </si>
+  <si>
+    <t>これで</t>
+  </si>
+  <si>
+    <t>1～20件目</t>
+  </si>
+  <si>
+    <t>LIMIT 20 OFFSET 0;　&lt; ページングの要</t>
+    <rPh sb="27" eb="28">
+      <t>カナメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>① WHERE組み立てる</t>
+  </si>
+  <si>
+    <t>② COUNT(*)取得</t>
+  </si>
+  <si>
+    <t>③ ORDER BY</t>
+  </si>
+  <si>
+    <t>④ LIMIT OFFSET</t>
+  </si>
+  <si>
+    <t>├─ price</t>
+  </si>
+  <si>
+    <t>├─ manufacturer</t>
+  </si>
+  <si>
+    <t>├─ name</t>
+  </si>
+  <si>
+    <t>└─ createdAt</t>
+  </si>
+  <si>
+    <t>と</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>├─ asc</t>
+  </si>
+  <si>
+    <t>└─ desc</t>
+  </si>
+  <si>
+    <t>を分ける？どうする？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エンドポイントイメージ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>order(asc or desc)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /public/api/v1/guitars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"items": [...],</t>
+  </si>
+  <si>
+    <t>"pageSize": 20,</t>
+  </si>
+  <si>
+    <t>"totalPages": 215</t>
   </si>
 </sst>
 </file>
@@ -7091,7 +7428,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7211,6 +7548,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -10752,6 +11092,436 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
+  <dimension ref="B2:P55"/>
+  <sheetFormatPr defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16">
+      <c r="B2" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="F4" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="F6" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="F8" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="I9" s="63"/>
+      <c r="M9" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="F10" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I10" s="63" t="s">
+        <v>1603</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I11" s="63" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="F12" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I12" s="63" t="s">
+        <v>1605</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="B13" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I13" s="63" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="F14" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="I14" s="63" t="s">
+        <v>1607</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="F15" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="F16" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I16" s="63" t="s">
+        <v>1628</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="F17" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>1629</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="F18" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="F19" s="1" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="F20" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="F21" s="1" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="F22" s="1" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="F23" s="1" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="F24" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="F25" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="63" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="F29" s="63" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I29" s="63" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F30" s="63" t="s">
+        <v>1635</v>
+      </c>
+      <c r="I30" s="63" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="63"/>
+      <c r="F31" s="63" t="s">
+        <v>1636</v>
+      </c>
+      <c r="I31" s="63" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="63" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F32" s="63" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="63" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F34" s="63" t="s">
+        <v>1638</v>
+      </c>
+      <c r="I34" s="63" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="F35" s="63" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="F36" s="63" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="F37" s="1" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="1" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G41" s="63" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G42" s="63" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G43" s="63" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G44" s="63" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G45" s="63" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="1" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="G47" s="1" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G48" s="63"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G49" s="63" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="G50" s="63" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G51" s="63" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="1" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B86953F-68C7-4A29-8F09-66E2D324A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A90AC96-CB22-4CB7-B176-09B59F5990BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -7171,10 +7171,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/manufacturers</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>SELECT *</t>
   </si>
   <si>
@@ -7253,6 +7249,10 @@
   </si>
   <si>
     <t>"totalPages": 215</t>
+  </si>
+  <si>
+    <t>GET /api/maker</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -11105,7 +11105,7 @@
         <v>1599</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>1654</v>
@@ -11114,7 +11114,7 @@
         <v>1609</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -11122,16 +11122,16 @@
         <v>1584</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1655</v>
+        <v>1679</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>1610</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -11145,7 +11145,7 @@
         <v>1611</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -11162,7 +11162,7 @@
         <v>1612</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -11251,7 +11251,7 @@
         <v>1606</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -11281,7 +11281,7 @@
         <v>1628</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -11292,7 +11292,7 @@
         <v>1629</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -11325,7 +11325,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -11348,7 +11348,7 @@
         <v>1610</v>
       </c>
       <c r="I29" s="63" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -11359,7 +11359,7 @@
         <v>1635</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -11368,7 +11368,7 @@
         <v>1636</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="32" spans="2:13">
@@ -11387,7 +11387,7 @@
         <v>1637</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -11398,7 +11398,7 @@
         <v>1638</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -11434,7 +11434,7 @@
         <v>1610</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="43" spans="2:9">
@@ -11442,7 +11442,7 @@
         <v>1644</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -11450,7 +11450,7 @@
         <v>1645</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -11458,7 +11458,7 @@
         <v>1646</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -11468,7 +11468,7 @@
     </row>
     <row r="47" spans="2:9">
       <c r="G47" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -11482,12 +11482,12 @@
         <v>1649</v>
       </c>
       <c r="G49" s="63" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="G50" s="63" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="51" spans="2:7">
@@ -11495,7 +11495,7 @@
         <v>1650</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="53" spans="2:7">
@@ -11503,7 +11503,7 @@
         <v>1651</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="54" spans="2:7">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A90AC96-CB22-4CB7-B176-09B59F5990BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF64FC6-D749-4E5B-9DE6-204CB9AEF9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -6985,15 +6985,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/series</t>
-  </si>
-  <si>
-    <t>GET /api/colors</t>
-  </si>
-  <si>
-    <t>GET /api/body-materials</t>
-  </si>
-  <si>
     <t>&lt;select&gt;</t>
   </si>
   <si>
@@ -7238,10 +7229,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /public/api/v1/guitars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>"items": [...],</t>
   </si>
   <si>
@@ -7251,7 +7238,23 @@
     <t>"totalPages": 215</t>
   </si>
   <si>
-    <t>GET /api/maker</t>
+    <t>GET /api/v1/guitars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/maker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/series</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/colors</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/body-materials</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11105,16 +11108,16 @@
         <v>1599</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -11125,13 +11128,13 @@
         <v>1675</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -11139,13 +11142,13 @@
         <v>1597</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1600</v>
+        <v>1677</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -11156,13 +11159,13 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1601</v>
+        <v>1678</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -11170,10 +11173,10 @@
         <v>1590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1602</v>
+        <v>1679</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -11184,7 +11187,7 @@
         <v>1591</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -11192,10 +11195,10 @@
         <v>1592</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -11207,7 +11210,7 @@
       </c>
       <c r="I9" s="63"/>
       <c r="M9" s="1" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -11215,10 +11218,10 @@
         <v>1594</v>
       </c>
       <c r="I10" s="63" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -11229,7 +11232,7 @@
         <v>1595</v>
       </c>
       <c r="I11" s="63" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -11237,10 +11240,10 @@
         <v>1596</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -11248,29 +11251,29 @@
         <v>1598</v>
       </c>
       <c r="I13" s="63" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="F14" s="1" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="I14" s="63" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="F15" s="1" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -11278,10 +11281,10 @@
         <v>1297</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -11289,231 +11292,231 @@
         <v>1291</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="F18" s="1" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="F19" s="1" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="F21" s="1" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="F25" s="1" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="63" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="F29" s="63" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I29" s="63" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="1" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="63"/>
       <c r="F31" s="63" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="63" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="F32" s="63" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="1" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="63" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="F34" s="63" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="F35" s="63" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="F36" s="63" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="37" spans="2:9">
       <c r="F37" s="1" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="1" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="G41" s="63" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="1" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45" s="1" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46" s="1" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="G47" s="1" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="G48" s="63"/>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="1" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="G49" s="63" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="G50" s="63" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="1" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
   </sheetData>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF64FC6-D749-4E5B-9DE6-204CB9AEF9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92B29C9-24AD-427B-97AD-AA705F4B9660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="1680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3759" uniqueCount="1684">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7242,10 +7242,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/v1/maker</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>GET /api/v1/series</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7255,6 +7251,26 @@
   </si>
   <si>
     <t>GET /api/v1/body-materials</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/makers</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>item</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"code": 1,</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"name": "ESP",</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"category": maker,</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11128,10 +11144,10 @@
         <v>1675</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1607</v>
+        <v>1680</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>1658</v>
@@ -11142,10 +11158,10 @@
         <v>1597</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>1659</v>
@@ -11159,10 +11175,10 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>1660</v>
@@ -11173,10 +11189,10 @@
         <v>1590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -11187,7 +11203,7 @@
         <v>1591</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -11198,7 +11214,7 @@
         <v>1605</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -11210,7 +11226,7 @@
       </c>
       <c r="I9" s="63"/>
       <c r="M9" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -11221,7 +11237,7 @@
         <v>1600</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -11234,6 +11250,9 @@
       <c r="I11" s="63" t="s">
         <v>1601</v>
       </c>
+      <c r="M11" s="1" t="s">
+        <v>1613</v>
+      </c>
     </row>
     <row r="12" spans="2:16">
       <c r="F12" s="1" t="s">
@@ -11242,9 +11261,6 @@
       <c r="I12" s="63" t="s">
         <v>1602</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>1607</v>
-      </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="1" t="s">
@@ -11254,7 +11270,7 @@
         <v>1603</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>1672</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -11265,7 +11281,7 @@
         <v>1604</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1615</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -11273,7 +11289,7 @@
         <v>1617</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -11284,7 +11300,7 @@
         <v>1625</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1673</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -11295,7 +11311,7 @@
         <v>1626</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -11303,13 +11319,16 @@
         <v>1618</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1613</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="F19" s="1" t="s">
         <v>1619</v>
       </c>
+      <c r="M19" s="1" t="s">
+        <v>1613</v>
+      </c>
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
@@ -11320,25 +11339,40 @@
       <c r="F21" s="1" t="s">
         <v>1621</v>
       </c>
+      <c r="M21" s="1" t="s">
+        <v>1607</v>
+      </c>
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
         <v>1624</v>
       </c>
+      <c r="M22" s="1" t="s">
+        <v>1683</v>
+      </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
         <v>1671</v>
       </c>
+      <c r="M23" s="1" t="s">
+        <v>1681</v>
+      </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
         <v>1622</v>
       </c>
+      <c r="M24" s="1" t="s">
+        <v>1682</v>
+      </c>
     </row>
     <row r="25" spans="2:13">
       <c r="F25" s="1" t="s">
         <v>1623</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>1613</v>
       </c>
     </row>
     <row r="28" spans="2:13">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92B29C9-24AD-427B-97AD-AA705F4B9660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CF8E94-2FF3-4A2A-97B3-E2228AB364E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3759" uniqueCount="1684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="1686">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7042,9 +7042,6 @@
     <t>"page": 1,</t>
   </si>
   <si>
-    <t>manufacturer</t>
-  </si>
-  <si>
     <t>bodyMaterial</t>
   </si>
   <si>
@@ -7118,18 +7115,12 @@
     <t>public class GuitarSearchRequest</t>
   </si>
   <si>
-    <t>public string? Manufacturer { get; set; }</t>
-  </si>
-  <si>
     <t>public string? Series { get; set; }</t>
   </si>
   <si>
     <t>public string? Color { get; set; }</t>
   </si>
   <si>
-    <t>public string? BodyMaterial { get; set; }</t>
-  </si>
-  <si>
     <t>public int? MinPrice { get; set; }</t>
   </si>
   <si>
@@ -7143,13 +7134,6 @@
   </si>
   <si>
     <t>public int PageSize { get; set; } = 20;</t>
-  </si>
-  <si>
-    <t>DTO案</t>
-    <rPh sb="3" eb="4">
-      <t>アン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>補助API(マスタ検索)</t>
@@ -7229,9 +7213,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>"items": [...],</t>
-  </si>
-  <si>
     <t>"pageSize": 20,</t>
   </si>
   <si>
@@ -7258,10 +7239,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>item</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>"code": 1,</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7271,6 +7248,41 @@
   </si>
   <si>
     <t>"category": maker,</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public string  Order { get; set; } = "ASC"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public string? Maker { get; set; }</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public int? BodyMaterialTop { get; set; }</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public int? BodyMaterialBack { get; set; }</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>public string? Name { get; set; }</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエスト案</t>
+    <rPh sb="5" eb="6">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>guitar</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"guitars": [...],</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11113,7 +11125,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
-  <dimension ref="B2:P55"/>
+  <dimension ref="B2:P57"/>
   <sheetFormatPr defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="8.796875" style="1"/>
@@ -11124,16 +11136,16 @@
         <v>1599</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>1606</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -11141,16 +11153,16 @@
         <v>1584</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -11158,13 +11170,13 @@
         <v>1597</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>1607</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -11175,13 +11187,13 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>1608</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -11189,7 +11201,7 @@
         <v>1590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>1609</v>
@@ -11275,18 +11287,18 @@
     </row>
     <row r="14" spans="2:16">
       <c r="F14" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="I14" s="63" t="s">
         <v>1604</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1672</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="F15" s="1" t="s">
-        <v>1617</v>
+        <v>1387</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>1615</v>
@@ -11297,7 +11309,7 @@
         <v>1297</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>1616</v>
@@ -11308,23 +11320,23 @@
         <v>1291</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="F18" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="F19" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>1613</v>
@@ -11332,12 +11344,12 @@
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="F21" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>1607</v>
@@ -11345,31 +11357,31 @@
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1683</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1681</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1682</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="F25" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>1613</v>
@@ -11377,7 +11389,7 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="63" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -11385,32 +11397,32 @@
         <v>1607</v>
       </c>
       <c r="I29" s="63" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="1" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="63"/>
       <c r="F31" s="63" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="63" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F32" s="63" t="s">
         <v>1613</v>
@@ -11418,52 +11430,52 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="1" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="63" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F34" s="63" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="F35" s="63" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="F36" s="63" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="37" spans="2:9">
       <c r="F37" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1650</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="G41" s="63" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -11471,85 +11483,98 @@
         <v>1607</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1641</v>
+        <v>1679</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1642</v>
+        <v>1682</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45" s="1" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46" s="1" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="47" spans="2:9">
+      <c r="B47" s="1" t="s">
+        <v>1680</v>
+      </c>
       <c r="G47" s="1" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1645</v>
+        <v>1681</v>
       </c>
       <c r="G48" s="63"/>
     </row>
     <row r="49" spans="2:7">
-      <c r="B49" s="1" t="s">
-        <v>1646</v>
-      </c>
       <c r="G49" s="63" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="50" spans="2:7">
+      <c r="B50" s="1" t="s">
+        <v>1642</v>
+      </c>
       <c r="G50" s="63" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1668</v>
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="1" t="s">
+        <v>1678</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1669</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="1" t="s">
-        <v>1649</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="1" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="1" t="s">
         <v>1613</v>
       </c>
     </row>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CF8E94-2FF3-4A2A-97B3-E2228AB364E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C1C6FA-AE1B-4942-AB16-73301069A414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -7066,9 +7066,6 @@
     <t>お遊びAPI</t>
   </si>
   <si>
-    <t>GET /api/guitars/random</t>
-  </si>
-  <si>
     <t>一般的なページング</t>
   </si>
   <si>
@@ -7283,6 +7280,10 @@
   </si>
   <si>
     <t>"guitars": [...],</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/guitars/random</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11136,16 +11137,16 @@
         <v>1599</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>1606</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -11153,16 +11154,16 @@
         <v>1584</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -11170,13 +11171,13 @@
         <v>1597</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>1607</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -11187,13 +11188,13 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>1608</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -11201,7 +11202,7 @@
         <v>1590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>1609</v>
@@ -11287,13 +11288,13 @@
     </row>
     <row r="14" spans="2:16">
       <c r="F14" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="I14" s="63" t="s">
         <v>1604</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -11320,10 +11321,10 @@
         <v>1291</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1625</v>
+        <v>1685</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -11331,7 +11332,7 @@
         <v>1617</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -11360,15 +11361,15 @@
         <v>1623</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -11376,7 +11377,7 @@
         <v>1621</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -11389,7 +11390,7 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="63" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -11397,32 +11398,32 @@
         <v>1607</v>
       </c>
       <c r="I29" s="63" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="63"/>
       <c r="F31" s="63" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="63" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F32" s="63" t="s">
         <v>1613</v>
@@ -11430,49 +11431,49 @@
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="1" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="63" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F34" s="63" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="F35" s="63" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="F36" s="63" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="37" spans="2:9">
       <c r="F37" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="G41" s="63" t="s">
         <v>1623</v>
@@ -11483,94 +11484,94 @@
         <v>1607</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46" s="1" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G48" s="63"/>
     </row>
     <row r="49" spans="2:7">
       <c r="G49" s="63" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="G50" s="63" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="57" spans="2:7">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C1C6FA-AE1B-4942-AB16-73301069A414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3561E78D-FAB3-4013-8E46-FCE9947F2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -7220,10 +7220,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/v1/series</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>GET /api/v1/colors</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7284,6 +7280,10 @@
   </si>
   <si>
     <t>GET /api/v1/guitars/random</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/series?maker=1</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11157,10 +11157,10 @@
         <v>1669</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>1653</v>
@@ -11171,7 +11171,7 @@
         <v>1597</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1670</v>
+        <v>1685</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>1607</v>
@@ -11188,7 +11188,7 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>1608</v>
@@ -11202,7 +11202,7 @@
         <v>1590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>1609</v>
@@ -11294,7 +11294,7 @@
         <v>1604</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -11321,7 +11321,7 @@
         <v>1291</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>1667</v>
@@ -11361,7 +11361,7 @@
         <v>1623</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -11369,7 +11369,7 @@
         <v>1666</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -11377,7 +11377,7 @@
         <v>1621</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -11468,7 +11468,7 @@
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -11489,7 +11489,7 @@
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="G43" s="63" t="s">
         <v>1657</v>
@@ -11497,7 +11497,7 @@
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G44" s="63" t="s">
         <v>1658</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>1660</v>
@@ -11526,7 +11526,7 @@
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G48" s="63"/>
     </row>
@@ -11553,7 +11553,7 @@
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="53" spans="2:7">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3561E78D-FAB3-4013-8E46-FCE9947F2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB7FAF8-4617-44B9-9A74-52D2118C5CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3764" uniqueCount="1688">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6937,15 +6937,6 @@
     <t>&amp;series=Stratocaster</t>
   </si>
   <si>
-    <t>&amp;color=Blue</t>
-  </si>
-  <si>
-    <t>&amp;bodyMaterial=Mahogany</t>
-  </si>
-  <si>
-    <t>&amp;name=player</t>
-  </si>
-  <si>
     <t>&amp;minPrice=100000</t>
   </si>
   <si>
@@ -6956,10 +6947,6 @@
   </si>
   <si>
     <t>&amp;pageSize=20</t>
-  </si>
-  <si>
-    <t>?maker=Fender</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>昇順 or 降順</t>
@@ -7224,10 +7211,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/v1/body-materials</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>GET /api/v1/makers</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7283,7 +7266,35 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/v1/series?maker=1</t>
+    <t>GET /api/v1/series?makerCd=1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&amp;colorCd=1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>?makerCd=1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&amp;bodyMaterialTopCd=1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&amp;name=xxx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&amp;bodyMaterialBackCd=1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/bodyMaterialsTop</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GET /api/v1/bodyMaterialsBack</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11134,19 +11145,19 @@
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" s="1" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -11154,30 +11165,30 @@
         <v>1584</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="4" spans="2:16">
       <c r="F4" s="1" t="s">
-        <v>1597</v>
+        <v>1682</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -11188,24 +11199,24 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="F6" s="1" t="s">
-        <v>1590</v>
+        <v>1681</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1671</v>
+        <v>1686</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1609</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -11213,21 +11224,24 @@
         <v>1586</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1591</v>
+        <v>1683</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1687</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="F8" s="1" t="s">
-        <v>1592</v>
+        <v>1685</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -11235,22 +11249,22 @@
         <v>1587</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1593</v>
+        <v>1684</v>
       </c>
       <c r="I9" s="63"/>
       <c r="M9" s="1" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="F10" s="1" t="s">
-        <v>1594</v>
+        <v>1590</v>
       </c>
       <c r="I10" s="63" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -11258,325 +11272,334 @@
         <v>1588</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="I11" s="63" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="F12" s="1" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>1602</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="1" t="s">
-        <v>1598</v>
+        <v>1594</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1593</v>
       </c>
       <c r="I13" s="63" t="s">
+        <v>1599</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>1607</v>
-      </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="F14" s="1" t="s">
-        <v>1637</v>
-      </c>
       <c r="I14" s="63" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="F15" s="1" t="s">
-        <v>1387</v>
+        <v>1633</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="F16" s="1" t="s">
-        <v>1297</v>
+        <v>1387</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="F17" s="1" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="F18" s="1" t="s">
-        <v>1617</v>
+        <v>1291</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="F19" s="1" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="F21" s="1" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1666</v>
+        <v>1619</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
-        <v>1621</v>
+        <v>1662</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="F25" s="1" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>1613</v>
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="F26" s="1" t="s">
+        <v>1618</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="63" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="29" spans="2:13">
-      <c r="F29" s="63" t="s">
-        <v>1607</v>
-      </c>
       <c r="I29" s="63" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="1" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>1630</v>
+        <v>1603</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="63"/>
       <c r="F31" s="63" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="63" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F32" s="63" t="s">
         <v>1627</v>
-      </c>
-      <c r="F32" s="63" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>1632</v>
+        <v>1624</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>1609</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="63" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F34" s="63" t="s">
-        <v>1633</v>
+        <v>1625</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>1628</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="F35" s="63" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="F36" s="63" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="F37" s="1" t="s">
-        <v>1636</v>
+      <c r="F37" s="63" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="F38" s="1" t="s">
+        <v>1632</v>
       </c>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="1" t="s">
-        <v>1638</v>
-      </c>
-      <c r="G41" s="63" t="s">
-        <v>1623</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="1" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1656</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45" s="1" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46" s="1" t="s">
-        <v>1640</v>
+        <v>1636</v>
+      </c>
+      <c r="G46" s="63" t="s">
+        <v>1655</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="1" t="s">
-        <v>1678</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>1660</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1679</v>
-      </c>
-      <c r="G48" s="63"/>
+        <v>1674</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>1656</v>
+      </c>
     </row>
     <row r="49" spans="2:7">
-      <c r="G49" s="63" t="s">
-        <v>1661</v>
-      </c>
+      <c r="G49" s="63"/>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="1" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="G50" s="63" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>1676</v>
+        <v>1671</v>
+      </c>
+      <c r="G52" s="63" t="s">
+        <v>1659</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>1643</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>1664</v>
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="G54" s="1" t="s">
+        <v>1660</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="1" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
     </row>
   </sheetData>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB7FAF8-4617-44B9-9A74-52D2118C5CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7344FA5B-1E33-4988-B54B-3FF6F80784E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3764" uniqueCount="1688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3763" uniqueCount="1687">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7290,11 +7290,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>GET /api/v1/bodyMaterialsTop</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>GET /api/v1/bodyMaterialsBack</t>
+    <t>GET /api/v1/bodyMaterials</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11226,9 +11222,6 @@
       <c r="F7" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>1687</v>
-      </c>
       <c r="M7" s="1" t="s">
         <v>1606</v>
       </c>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7344FA5B-1E33-4988-B54B-3FF6F80784E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DE52FF-0FFA-4407-A081-AADCAF93EB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3763" uniqueCount="1687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3765" uniqueCount="1689">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7164,15 +7165,9 @@
     <t>├─ price</t>
   </si>
   <si>
-    <t>├─ manufacturer</t>
-  </si>
-  <si>
     <t>├─ name</t>
   </si>
   <si>
-    <t>└─ createdAt</t>
-  </si>
-  <si>
     <t>と</t>
   </si>
   <si>
@@ -7183,10 +7178,6 @@
   </si>
   <si>
     <t>└─ desc</t>
-  </si>
-  <si>
-    <t>を分ける？どうする？</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>エンドポイントイメージ</t>
@@ -7291,6 +7282,29 @@
   </si>
   <si>
     <t>GET /api/v1/bodyMaterials</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>├─ maker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">└─ </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>を分ける？どうする？ &gt; 分ける。</t>
+    <rPh sb="13" eb="14">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"hasPrev": bool</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"hasNext": bool</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11144,7 +11158,7 @@
         <v>1595</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>1642</v>
@@ -11161,13 +11175,13 @@
         <v>1584</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>1649</v>
@@ -11175,10 +11189,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="F4" s="1" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>1603</v>
@@ -11195,7 +11209,7 @@
         <v>1589</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>1604</v>
@@ -11206,10 +11220,10 @@
     </row>
     <row r="6" spans="2:16">
       <c r="F6" s="1" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>1605</v>
@@ -11220,7 +11234,7 @@
         <v>1586</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>1606</v>
@@ -11228,7 +11242,7 @@
     </row>
     <row r="8" spans="2:16">
       <c r="F8" s="1" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>1601</v>
@@ -11242,7 +11256,7 @@
         <v>1587</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="I9" s="63"/>
       <c r="M9" s="1" t="s">
@@ -11301,7 +11315,7 @@
         <v>1600</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -11328,10 +11342,10 @@
         <v>1297</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -11339,7 +11353,7 @@
         <v>1291</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -11347,44 +11361,44 @@
         <v>1613</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1609</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
         <v>1614</v>
       </c>
+      <c r="M20" s="1" t="s">
+        <v>1688</v>
+      </c>
     </row>
     <row r="21" spans="2:13">
       <c r="F21" s="1" t="s">
         <v>1615</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>1670</v>
-      </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1668</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -11392,12 +11406,20 @@
         <v>1617</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>1609</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="F26" s="1" t="s">
         <v>1618</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="M27" s="1" t="s">
+        <v>1609</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11482,7 +11504,7 @@
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -11500,7 +11522,7 @@
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="G43" s="63" t="s">
         <v>1652</v>
@@ -11508,10 +11530,10 @@
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1653</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -11519,7 +11541,7 @@
         <v>1635</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -11527,20 +11549,20 @@
         <v>1636</v>
       </c>
       <c r="G46" s="63" t="s">
-        <v>1655</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="1" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="49" spans="2:7">
@@ -11551,7 +11573,7 @@
         <v>1637</v>
       </c>
       <c r="G50" s="63" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="51" spans="2:7">
@@ -11559,15 +11581,15 @@
         <v>1638</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G52" s="63" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="53" spans="2:7">
@@ -11577,7 +11599,7 @@
     </row>
     <row r="54" spans="2:7">
       <c r="G54" s="1" t="s">
-        <v>1660</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="55" spans="2:7">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DE52FF-0FFA-4407-A081-AADCAF93EB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E3558-AE44-4DCA-A149-8A4E998BACA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="各種設定" sheetId="8" r:id="rId8"/>
     <sheet name="guitarCrawler" sheetId="9" r:id="rId9"/>
     <sheet name="public API" sheetId="10" r:id="rId10"/>
+    <sheet name="guiatr gallery" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3765" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="1718">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7305,6 +7306,196 @@
   </si>
   <si>
     <t>"hasNext": bool</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>guitar image</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>guitar name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>価格：xxx,xxx円（税抜）</t>
+    <rPh sb="0" eb="2">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゼイヌ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・・・</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソート [ maker ▼ ]</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>〇昇順　〇降順</t>
+    <rPh sb="1" eb="3">
+      <t>ショウジュン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウジュン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一覧ページ</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>＜</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メーカーにより内容が変動</t>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>optionはベタ書き</t>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>詳細ページ</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>guitar spec</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>maker</t>
+  </si>
+  <si>
+    <t>scale_length_mm</t>
+  </si>
+  <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>(comment) ….......................................</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…..........................................................</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>:</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>brack pearl</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Price:</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> xxx,xxx円（税抜）</t>
+  </si>
+  <si>
+    <t>alt = guitarName</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HORIZON-I</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>閉じる</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>枠の外をクリックしても閉じる</t>
+    <rPh sb="0" eb="1">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>◀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　１　２　３　４　５　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>…　▶</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1 - 25 / 283　件</t>
+    <rPh sb="13" eb="14">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>clickで詳細モーダル表示</t>
+    <rPh sb="6" eb="8">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7315,7 +7506,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7365,6 +7556,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -7404,7 +7608,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -7473,6 +7677,166 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -7481,7 +7845,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7604,6 +7968,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -11623,6 +12013,641 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
+  <dimension ref="B2:R45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="13" max="13" width="8.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="18.600000000000001" thickBot="1">
+      <c r="E2" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18">
+      <c r="F3" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I3" s="76"/>
+      <c r="J3" s="70" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K3" s="71"/>
+      <c r="L3" s="72"/>
+      <c r="N3" s="70" t="s">
+        <v>1689</v>
+      </c>
+      <c r="O3" s="71"/>
+      <c r="P3" s="72"/>
+    </row>
+    <row r="4" spans="2:18">
+      <c r="F4" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I4" s="76"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="75"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="75"/>
+    </row>
+    <row r="5" spans="2:18">
+      <c r="F5" s="1"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="73" t="s">
+        <v>1717</v>
+      </c>
+      <c r="K5" s="74"/>
+      <c r="L5" s="75"/>
+      <c r="N5" s="73" t="s">
+        <v>1717</v>
+      </c>
+      <c r="O5" s="74"/>
+      <c r="P5" s="75"/>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="I6" s="76"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="75"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="75"/>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="F7" s="1"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="75"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="75"/>
+      <c r="R7" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="F8" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="I8" s="76"/>
+      <c r="J8" s="64" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K8" s="65"/>
+      <c r="L8" s="66"/>
+      <c r="N8" s="64" t="s">
+        <v>1690</v>
+      </c>
+      <c r="O8" s="65"/>
+      <c r="P8" s="66"/>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="F9" s="1"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="64" t="s">
+        <v>1691</v>
+      </c>
+      <c r="K9" s="65"/>
+      <c r="L9" s="66"/>
+      <c r="N9" s="64" t="s">
+        <v>1691</v>
+      </c>
+      <c r="O9" s="65"/>
+      <c r="P9" s="66"/>
+    </row>
+    <row r="10" spans="2:18" ht="18.600000000000001" thickBot="1">
+      <c r="F10" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="I10" s="76"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="69"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="69"/>
+    </row>
+    <row r="11" spans="2:18">
+      <c r="F11" s="1"/>
+      <c r="I11" s="76"/>
+    </row>
+    <row r="12" spans="2:18">
+      <c r="F12" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="I12" s="76"/>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="F13" s="1"/>
+      <c r="I13" s="76"/>
+      <c r="J13" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="I14" s="76"/>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="I15" s="76"/>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="F16" t="s">
+        <v>1694</v>
+      </c>
+      <c r="I16" s="76"/>
+    </row>
+    <row r="17" spans="4:15">
+      <c r="I17" s="76"/>
+      <c r="J17" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15">
+      <c r="I18" s="76"/>
+    </row>
+    <row r="19" spans="4:15">
+      <c r="I19" s="76"/>
+      <c r="J19" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15">
+      <c r="E21" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="22" spans="4:15" ht="18.600000000000001" thickBot="1">
+      <c r="D22" s="81"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="83"/>
+      <c r="O22" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="23" spans="4:15">
+      <c r="D23" s="84"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65" t="s">
+        <v>1700</v>
+      </c>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="85"/>
+    </row>
+    <row r="24" spans="4:15">
+      <c r="D24" s="84"/>
+      <c r="E24" s="73" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="85"/>
+    </row>
+    <row r="25" spans="4:15">
+      <c r="D25" s="84"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="77" t="s">
+        <v>1701</v>
+      </c>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M25" s="77" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N25" s="85"/>
+    </row>
+    <row r="26" spans="4:15">
+      <c r="D26" s="84"/>
+      <c r="E26" s="73" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="77" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K26" s="77"/>
+      <c r="L26" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M26" s="77" t="s">
+        <v>1712</v>
+      </c>
+      <c r="N26" s="85"/>
+    </row>
+    <row r="27" spans="4:15">
+      <c r="D27" s="84"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="77" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K27" s="77"/>
+      <c r="L27" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M27" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N27" s="85"/>
+    </row>
+    <row r="28" spans="4:15">
+      <c r="D28" s="84"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="77" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K28" s="77"/>
+      <c r="L28" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M28" s="77" t="s">
+        <v>1708</v>
+      </c>
+      <c r="N28" s="85"/>
+    </row>
+    <row r="29" spans="4:15">
+      <c r="D29" s="84"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="77" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M29" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N29" s="85"/>
+    </row>
+    <row r="30" spans="4:15" ht="18.600000000000001" thickBot="1">
+      <c r="D30" s="84"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="77" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M30" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N30" s="85"/>
+    </row>
+    <row r="31" spans="4:15">
+      <c r="D31" s="84"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="77" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M31" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N31" s="85"/>
+    </row>
+    <row r="32" spans="4:15">
+      <c r="D32" s="84"/>
+      <c r="E32" s="65" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F32" s="65" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="77" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M32" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N32" s="85"/>
+    </row>
+    <row r="33" spans="4:14">
+      <c r="D33" s="84"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="77" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M33" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N33" s="85"/>
+    </row>
+    <row r="34" spans="4:14">
+      <c r="D34" s="84"/>
+      <c r="E34" s="65" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="77" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M34" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N34" s="85"/>
+    </row>
+    <row r="35" spans="4:14">
+      <c r="D35" s="84"/>
+      <c r="E35" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="77" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K35" s="77"/>
+      <c r="L35" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M35" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N35" s="85"/>
+    </row>
+    <row r="36" spans="4:14">
+      <c r="D36" s="84"/>
+      <c r="E36" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="77" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K36" s="77"/>
+      <c r="L36" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M36" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N36" s="85"/>
+    </row>
+    <row r="37" spans="4:14">
+      <c r="D37" s="84"/>
+      <c r="E37" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="77" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K37" s="77"/>
+      <c r="L37" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M37" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N37" s="85"/>
+    </row>
+    <row r="38" spans="4:14">
+      <c r="D38" s="84"/>
+      <c r="E38" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="77" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K38" s="77"/>
+      <c r="L38" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M38" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N38" s="85"/>
+    </row>
+    <row r="39" spans="4:14">
+      <c r="D39" s="84"/>
+      <c r="E39" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="77" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M39" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N39" s="85"/>
+    </row>
+    <row r="40" spans="4:14">
+      <c r="D40" s="84"/>
+      <c r="E40" s="65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="77" t="s">
+        <v>1703</v>
+      </c>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M40" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N40" s="85"/>
+    </row>
+    <row r="41" spans="4:14">
+      <c r="D41" s="84"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="77" t="s">
+        <v>1704</v>
+      </c>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M41" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="N41" s="85"/>
+    </row>
+    <row r="42" spans="4:14">
+      <c r="D42" s="84"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="85"/>
+    </row>
+    <row r="43" spans="4:14">
+      <c r="D43" s="84"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="89" t="s">
+        <v>1713</v>
+      </c>
+      <c r="N43" s="85"/>
+    </row>
+    <row r="44" spans="4:14">
+      <c r="D44" s="84"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="85"/>
+    </row>
+    <row r="45" spans="4:14">
+      <c r="D45" s="86"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="87"/>
+      <c r="I45" s="87"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="87"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="88"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E3558-AE44-4DCA-A149-8A4E998BACA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A91EED-E521-4F6C-A814-2BFE1A5A8C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3857" uniqueCount="1719">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7495,6 +7495,13 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>検索</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -7570,7 +7577,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7607,8 +7614,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -7837,6 +7850,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -7845,7 +7895,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7994,6 +8044,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -12021,52 +12077,70 @@
     <col min="13" max="13" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="2" spans="2:18">
       <c r="E2" t="s">
         <v>1695</v>
       </c>
-    </row>
-    <row r="3" spans="2:18">
-      <c r="F3" s="1" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+    </row>
+    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
+      <c r="F3" s="90" t="s">
         <v>1595</v>
       </c>
-      <c r="I3" s="76"/>
-      <c r="J3" s="70" t="s">
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="83"/>
+    </row>
+    <row r="4" spans="2:18">
+      <c r="F4" s="92" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="70" t="s">
         <v>1689</v>
       </c>
-      <c r="K3" s="71"/>
-      <c r="L3" s="72"/>
-      <c r="N3" s="70" t="s">
+      <c r="K4" s="71"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="70" t="s">
         <v>1689</v>
       </c>
-      <c r="O3" s="71"/>
-      <c r="P3" s="72"/>
-    </row>
-    <row r="4" spans="2:18">
-      <c r="F4" s="1" t="s">
-        <v>1584</v>
-      </c>
-      <c r="I4" s="76"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="75"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="75"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="85"/>
     </row>
     <row r="5" spans="2:18">
-      <c r="F5" s="1"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="76"/>
-      <c r="J5" s="73" t="s">
-        <v>1717</v>
-      </c>
+      <c r="J5" s="73"/>
       <c r="K5" s="74"/>
       <c r="L5" s="75"/>
-      <c r="N5" s="73" t="s">
-        <v>1717</v>
-      </c>
+      <c r="M5" s="65"/>
+      <c r="N5" s="73"/>
       <c r="O5" s="74"/>
       <c r="P5" s="75"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="85"/>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" t="s">
@@ -12075,88 +12149,148 @@
       <c r="E6" t="s">
         <v>1696</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="92" t="s">
         <v>1585</v>
       </c>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
       <c r="I6" s="76"/>
-      <c r="J6" s="73"/>
+      <c r="J6" s="73" t="s">
+        <v>1717</v>
+      </c>
       <c r="K6" s="74"/>
       <c r="L6" s="75"/>
-      <c r="N6" s="73"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="73" t="s">
+        <v>1717</v>
+      </c>
       <c r="O6" s="74"/>
       <c r="P6" s="75"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="85"/>
     </row>
     <row r="7" spans="2:18">
-      <c r="F7" s="1"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="76"/>
       <c r="J7" s="73"/>
       <c r="K7" s="74"/>
       <c r="L7" s="75"/>
+      <c r="M7" s="65"/>
       <c r="N7" s="73"/>
       <c r="O7" s="74"/>
       <c r="P7" s="75"/>
-      <c r="R7" t="s">
+      <c r="Q7" s="65"/>
+      <c r="R7" s="85" t="s">
         <v>1692</v>
       </c>
     </row>
     <row r="8" spans="2:18">
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="92" t="s">
         <v>1586</v>
       </c>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
       <c r="I8" s="76"/>
-      <c r="J8" s="64" t="s">
-        <v>1690</v>
-      </c>
-      <c r="K8" s="65"/>
-      <c r="L8" s="66"/>
-      <c r="N8" s="64" t="s">
-        <v>1690</v>
-      </c>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="85"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="F9" s="1"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
       <c r="I9" s="76"/>
       <c r="J9" s="64" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="66"/>
+      <c r="M9" s="65"/>
       <c r="N9" s="64" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="O9" s="65"/>
       <c r="P9" s="66"/>
-    </row>
-    <row r="10" spans="2:18" ht="18.600000000000001" thickBot="1">
-      <c r="F10" s="1" t="s">
+      <c r="Q9" s="65"/>
+      <c r="R9" s="85"/>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="F10" s="92" t="s">
         <v>1587</v>
       </c>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
       <c r="I10" s="76"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="69"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="69"/>
-    </row>
-    <row r="11" spans="2:18">
-      <c r="F11" s="1"/>
+      <c r="J10" s="64" t="s">
+        <v>1691</v>
+      </c>
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="64" t="s">
+        <v>1691</v>
+      </c>
+      <c r="O10" s="65"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="85"/>
+    </row>
+    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
+      <c r="F11" s="92"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
       <c r="I11" s="76"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="85"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="92" t="s">
         <v>1588</v>
       </c>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="76"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="F13" s="1"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
       <c r="I13" s="76"/>
-      <c r="J13" t="s">
+      <c r="J13" s="65" t="s">
         <v>1692</v>
       </c>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="85"/>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -12165,41 +12299,111 @@
       <c r="E14" t="s">
         <v>1696</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="92" t="s">
         <v>1693</v>
       </c>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
       <c r="I14" s="76"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="2:18">
+      <c r="F15" s="84"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="76"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="F16" t="s">
+      <c r="F16" s="84" t="s">
         <v>1694</v>
       </c>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
       <c r="I16" s="76"/>
-    </row>
-    <row r="17" spans="4:15">
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="85"/>
+    </row>
+    <row r="17" spans="4:18">
+      <c r="F17" s="84"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
       <c r="I17" s="76"/>
-      <c r="J17" t="s">
+      <c r="J17" s="65" t="s">
         <v>1716</v>
       </c>
-    </row>
-    <row r="18" spans="4:15">
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="85"/>
+    </row>
+    <row r="18" spans="4:18">
+      <c r="F18" s="84"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="95" t="s">
+        <v>1718</v>
+      </c>
       <c r="I18" s="76"/>
-    </row>
-    <row r="19" spans="4:15">
-      <c r="I19" s="76"/>
-      <c r="J19" t="s">
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="85"/>
+    </row>
+    <row r="19" spans="4:18">
+      <c r="F19" s="86"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="87" t="s">
         <v>1715</v>
       </c>
-    </row>
-    <row r="21" spans="4:15">
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="87"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+    </row>
+    <row r="21" spans="4:18">
       <c r="E21" t="s">
         <v>1699</v>
       </c>
     </row>
-    <row r="22" spans="4:15" ht="18.600000000000001" thickBot="1">
+    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D22" s="81"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
@@ -12215,7 +12419,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="23" spans="4:15">
+    <row r="23" spans="4:18">
       <c r="D23" s="84"/>
       <c r="E23" s="70"/>
       <c r="F23" s="71"/>
@@ -12230,7 +12434,7 @@
       <c r="M23" s="65"/>
       <c r="N23" s="85"/>
     </row>
-    <row r="24" spans="4:15">
+    <row r="24" spans="4:18">
       <c r="D24" s="84"/>
       <c r="E24" s="73" t="s">
         <v>1689</v>
@@ -12245,7 +12449,7 @@
       <c r="M24" s="65"/>
       <c r="N24" s="85"/>
     </row>
-    <row r="25" spans="4:15">
+    <row r="25" spans="4:18">
       <c r="D25" s="84"/>
       <c r="E25" s="73"/>
       <c r="F25" s="74"/>
@@ -12264,7 +12468,7 @@
       </c>
       <c r="N25" s="85"/>
     </row>
-    <row r="26" spans="4:15">
+    <row r="26" spans="4:18">
       <c r="D26" s="84"/>
       <c r="E26" s="73" t="s">
         <v>1711</v>
@@ -12285,7 +12489,7 @@
       </c>
       <c r="N26" s="85"/>
     </row>
-    <row r="27" spans="4:15">
+    <row r="27" spans="4:18">
       <c r="D27" s="84"/>
       <c r="E27" s="73"/>
       <c r="F27" s="74"/>
@@ -12304,7 +12508,7 @@
       </c>
       <c r="N27" s="85"/>
     </row>
-    <row r="28" spans="4:15">
+    <row r="28" spans="4:18">
       <c r="D28" s="84"/>
       <c r="E28" s="73"/>
       <c r="F28" s="74"/>
@@ -12323,7 +12527,7 @@
       </c>
       <c r="N28" s="85"/>
     </row>
-    <row r="29" spans="4:15">
+    <row r="29" spans="4:18">
       <c r="D29" s="84"/>
       <c r="E29" s="73"/>
       <c r="F29" s="74"/>
@@ -12342,7 +12546,7 @@
       </c>
       <c r="N29" s="85"/>
     </row>
-    <row r="30" spans="4:15" ht="18.600000000000001" thickBot="1">
+    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D30" s="84"/>
       <c r="E30" s="78"/>
       <c r="F30" s="79"/>
@@ -12361,7 +12565,7 @@
       </c>
       <c r="N30" s="85"/>
     </row>
-    <row r="31" spans="4:15">
+    <row r="31" spans="4:18">
       <c r="D31" s="84"/>
       <c r="E31" s="65"/>
       <c r="F31" s="65"/>
@@ -12380,7 +12584,7 @@
       </c>
       <c r="N31" s="85"/>
     </row>
-    <row r="32" spans="4:15">
+    <row r="32" spans="4:18">
       <c r="D32" s="84"/>
       <c r="E32" s="65" t="s">
         <v>1709</v>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A91EED-E521-4F6C-A814-2BFE1A5A8C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A230908B-C406-4C74-BC0A-0233EEDC9353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3857" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3853" uniqueCount="1718">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -6530,13 +6529,6 @@
   </si>
   <si>
     <t>明るく硬質でクセのあるトーン。</t>
-  </si>
-  <si>
-    <t>省略</t>
-    <rPh sb="0" eb="2">
-      <t>ショウリャク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>対象CD</t>
@@ -7895,7 +7887,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8019,7 +8011,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -8028,7 +8019,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -8048,7 +8039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -11601,175 +11592,175 @@
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="1" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="4" spans="2:16">
       <c r="F4" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="1" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="F6" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="F8" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="I9" s="63"/>
       <c r="M9" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="F10" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="I10" s="63" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="I11" s="63" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="F12" s="1" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" s="1" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="I13" s="63" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="I14" s="63" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="F15" s="1" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -11777,10 +11768,10 @@
         <v>1387</v>
       </c>
       <c r="I16" s="63" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -11788,10 +11779,10 @@
         <v>1297</v>
       </c>
       <c r="I17" s="63" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -11799,216 +11790,216 @@
         <v>1291</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="F19" s="1" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="F20" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="F21" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="F22" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="F23" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="F24" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="F25" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="F26" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="M27" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="63" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="I29" s="63" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="I30" s="63" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="63"/>
       <c r="F31" s="63" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="63" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F32" s="63" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F33" s="63" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="63" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I34" s="63" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="F35" s="63" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="F36" s="63" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="37" spans="2:9">
       <c r="F37" s="63" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="38" spans="2:9">
       <c r="F38" s="1" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="1" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G42" s="63" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="G43" s="63" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="G44" s="63" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="B45" s="1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="46" spans="2:9">
       <c r="B46" s="1" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="G46" s="63" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="49" spans="2:7">
@@ -12016,51 +12007,51 @@
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="G50" s="63" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="G51" s="63" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="G52" s="63" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="54" spans="2:7">
       <c r="G54" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
   </sheetData>
@@ -12079,772 +12070,582 @@
   <sheetData>
     <row r="2" spans="2:18">
       <c r="E2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+        <v>1694</v>
+      </c>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
-      <c r="F3" s="90" t="s">
-        <v>1595</v>
-      </c>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="83"/>
+      <c r="F3" s="89" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="82"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="F4" s="92" t="s">
-        <v>1584</v>
-      </c>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="70" t="s">
-        <v>1689</v>
-      </c>
-      <c r="K4" s="71"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="70" t="s">
-        <v>1689</v>
-      </c>
-      <c r="O4" s="71"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="85"/>
+      <c r="F4" s="91" t="s">
+        <v>1583</v>
+      </c>
+      <c r="I4" s="75"/>
+      <c r="J4" s="69" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="N4" s="69" t="s">
+        <v>1688</v>
+      </c>
+      <c r="O4" s="70"/>
+      <c r="P4" s="71"/>
+      <c r="R4" s="84"/>
     </row>
     <row r="5" spans="2:18">
-      <c r="F5" s="92"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="85"/>
+      <c r="F5" s="91"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="74"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="74"/>
+      <c r="R5" s="84"/>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E6" t="s">
-        <v>1696</v>
-      </c>
-      <c r="F6" s="92" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F6" s="91" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I6" s="75"/>
+      <c r="J6" s="72" t="s">
+        <v>1716</v>
+      </c>
+      <c r="K6" s="73"/>
+      <c r="L6" s="74"/>
+      <c r="N6" s="72" t="s">
+        <v>1716</v>
+      </c>
+      <c r="O6" s="73"/>
+      <c r="P6" s="74"/>
+      <c r="R6" s="84"/>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="F7" s="91"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="74"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="74"/>
+      <c r="R7" s="84" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="F8" s="91" t="s">
         <v>1585</v>
       </c>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="73" t="s">
-        <v>1717</v>
-      </c>
-      <c r="K6" s="74"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="73" t="s">
-        <v>1717</v>
-      </c>
-      <c r="O6" s="74"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="85"/>
-    </row>
-    <row r="7" spans="2:18">
-      <c r="F7" s="92"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="85" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18">
-      <c r="F8" s="92" t="s">
+      <c r="I8" s="75"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="74"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="74"/>
+      <c r="R8" s="84"/>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="F9" s="91"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="64" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L9" s="65"/>
+      <c r="N9" s="64" t="s">
+        <v>1689</v>
+      </c>
+      <c r="P9" s="65"/>
+      <c r="R9" s="84"/>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="F10" s="91" t="s">
         <v>1586</v>
       </c>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="65"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="75"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="85"/>
-    </row>
-    <row r="9" spans="2:18">
-      <c r="F9" s="92"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="64" t="s">
+      <c r="I10" s="75"/>
+      <c r="J10" s="64" t="s">
         <v>1690</v>
       </c>
-      <c r="K9" s="65"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="64" t="s">
+      <c r="L10" s="65"/>
+      <c r="N10" s="64" t="s">
         <v>1690</v>
       </c>
-      <c r="O9" s="65"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="85"/>
-    </row>
-    <row r="10" spans="2:18">
-      <c r="F10" s="92" t="s">
+      <c r="P10" s="65"/>
+      <c r="R10" s="84"/>
+    </row>
+    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
+      <c r="F11" s="91"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="68"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="68"/>
+      <c r="R11" s="84"/>
+    </row>
+    <row r="12" spans="2:18">
+      <c r="F12" s="91" t="s">
         <v>1587</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="64" t="s">
+      <c r="I12" s="75"/>
+      <c r="R12" s="84"/>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="F13" s="91"/>
+      <c r="I13" s="75"/>
+      <c r="J13" t="s">
         <v>1691</v>
       </c>
-      <c r="K10" s="65"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="64" t="s">
-        <v>1691</v>
-      </c>
-      <c r="O10" s="65"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="85"/>
-    </row>
-    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
-      <c r="F11" s="92"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="85"/>
-    </row>
-    <row r="12" spans="2:18">
-      <c r="F12" s="92" t="s">
-        <v>1588</v>
-      </c>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="85"/>
-    </row>
-    <row r="13" spans="2:18">
-      <c r="F13" s="92"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="65" t="s">
-        <v>1692</v>
-      </c>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="85"/>
+      <c r="R13" s="84"/>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E14" t="s">
-        <v>1696</v>
-      </c>
-      <c r="F14" s="92" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F14" s="91" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I14" s="75"/>
+      <c r="R14" s="84"/>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="F15" s="83"/>
+      <c r="I15" s="75"/>
+      <c r="R15" s="84"/>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="F16" s="83" t="s">
         <v>1693</v>
       </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="85"/>
-    </row>
-    <row r="15" spans="2:18">
-      <c r="F15" s="84"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="85"/>
-    </row>
-    <row r="16" spans="2:18">
-      <c r="F16" s="84" t="s">
-        <v>1694</v>
-      </c>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="65"/>
-      <c r="L16" s="65"/>
-      <c r="M16" s="65"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="65"/>
-      <c r="P16" s="65"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="85"/>
+      <c r="I16" s="75"/>
+      <c r="R16" s="84"/>
     </row>
     <row r="17" spans="4:18">
-      <c r="F17" s="84"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="65" t="s">
-        <v>1716</v>
-      </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="85"/>
+      <c r="F17" s="83"/>
+      <c r="I17" s="75"/>
+      <c r="J17" t="s">
+        <v>1715</v>
+      </c>
+      <c r="R17" s="84"/>
     </row>
     <row r="18" spans="4:18">
-      <c r="F18" s="84"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="95" t="s">
-        <v>1718</v>
-      </c>
-      <c r="I18" s="76"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="85"/>
+      <c r="F18" s="83"/>
+      <c r="H18" s="94" t="s">
+        <v>1717</v>
+      </c>
+      <c r="I18" s="75"/>
+      <c r="R18" s="84"/>
     </row>
     <row r="19" spans="4:18">
-      <c r="F19" s="86"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="87" t="s">
-        <v>1715</v>
-      </c>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="87"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="88"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="86" t="s">
+        <v>1714</v>
+      </c>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="86"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="87"/>
     </row>
     <row r="21" spans="4:18">
       <c r="E21" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="82"/>
+      <c r="O22" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="23" spans="4:18">
+      <c r="D23" s="83"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="71"/>
+      <c r="J23" t="s">
         <v>1699</v>
       </c>
-    </row>
-    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
-      <c r="D22" s="81"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="83"/>
-      <c r="O22" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="23" spans="4:18">
-      <c r="D23" s="84"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65" t="s">
+      <c r="N23" s="84"/>
+    </row>
+    <row r="24" spans="4:18">
+      <c r="D24" s="83"/>
+      <c r="E24" s="72" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="74"/>
+      <c r="N24" s="84"/>
+    </row>
+    <row r="25" spans="4:18">
+      <c r="D25" s="83"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
+      <c r="J25" s="76" t="s">
         <v>1700</v>
       </c>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="85"/>
-    </row>
-    <row r="24" spans="4:18">
-      <c r="D24" s="84"/>
-      <c r="E24" s="73" t="s">
-        <v>1689</v>
-      </c>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="85"/>
-    </row>
-    <row r="25" spans="4:18">
-      <c r="D25" s="84"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="77" t="s">
+      <c r="K25" s="76"/>
+      <c r="L25" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M25" s="76" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N25" s="84"/>
+    </row>
+    <row r="26" spans="4:18">
+      <c r="D26" s="83"/>
+      <c r="E26" s="72" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
+      <c r="J26" s="76" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K26" s="76"/>
+      <c r="L26" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M26" s="76" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N26" s="84"/>
+    </row>
+    <row r="27" spans="4:18">
+      <c r="D27" s="83"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="74"/>
+      <c r="J27" s="76" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M27" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N27" s="84"/>
+    </row>
+    <row r="28" spans="4:18">
+      <c r="D28" s="83"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="74"/>
+      <c r="J28" s="76" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M28" s="76" t="s">
+        <v>1707</v>
+      </c>
+      <c r="N28" s="84"/>
+    </row>
+    <row r="29" spans="4:18">
+      <c r="D29" s="83"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="74"/>
+      <c r="J29" s="76" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K29" s="76"/>
+      <c r="L29" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M29" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N29" s="84"/>
+    </row>
+    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
+      <c r="D30" s="83"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="79"/>
+      <c r="J30" s="76" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K30" s="76"/>
+      <c r="L30" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M30" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N30" s="84"/>
+    </row>
+    <row r="31" spans="4:18">
+      <c r="D31" s="83"/>
+      <c r="J31" s="76" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K31" s="76"/>
+      <c r="L31" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M31" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N31" s="84"/>
+    </row>
+    <row r="32" spans="4:18">
+      <c r="D32" s="83"/>
+      <c r="E32" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1709</v>
+      </c>
+      <c r="J32" s="76" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K32" s="76"/>
+      <c r="L32" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M32" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N32" s="84"/>
+    </row>
+    <row r="33" spans="4:14">
+      <c r="D33" s="83"/>
+      <c r="J33" s="76" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K33" s="76"/>
+      <c r="L33" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M33" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N33" s="84"/>
+    </row>
+    <row r="34" spans="4:14">
+      <c r="D34" s="83"/>
+      <c r="E34" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J34" s="76" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K34" s="76"/>
+      <c r="L34" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M34" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N34" s="84"/>
+    </row>
+    <row r="35" spans="4:14">
+      <c r="D35" s="83"/>
+      <c r="E35" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J35" s="76" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K35" s="76"/>
+      <c r="L35" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M35" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N35" s="84"/>
+    </row>
+    <row r="36" spans="4:14">
+      <c r="D36" s="83"/>
+      <c r="E36" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J36" s="76" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M36" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N36" s="84"/>
+    </row>
+    <row r="37" spans="4:14">
+      <c r="D37" s="83"/>
+      <c r="E37" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J37" s="76" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M37" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N37" s="84"/>
+    </row>
+    <row r="38" spans="4:14">
+      <c r="D38" s="83"/>
+      <c r="E38" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J38" s="76" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M38" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N38" s="84"/>
+    </row>
+    <row r="39" spans="4:14">
+      <c r="D39" s="83"/>
+      <c r="E39" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J39" s="76" t="s">
         <v>1701</v>
       </c>
-      <c r="K25" s="77"/>
-      <c r="L25" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M25" s="77" t="s">
-        <v>1183</v>
-      </c>
-      <c r="N25" s="85"/>
-    </row>
-    <row r="26" spans="4:18">
-      <c r="D26" s="84"/>
-      <c r="E26" s="73" t="s">
-        <v>1711</v>
-      </c>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="77" t="s">
-        <v>1614</v>
-      </c>
-      <c r="K26" s="77"/>
-      <c r="L26" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M26" s="77" t="s">
+      <c r="K39" s="76"/>
+      <c r="L39" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M39" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N39" s="84"/>
+    </row>
+    <row r="40" spans="4:14">
+      <c r="D40" s="83"/>
+      <c r="E40" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J40" s="76" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K40" s="76"/>
+      <c r="L40" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M40" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N40" s="84"/>
+    </row>
+    <row r="41" spans="4:14">
+      <c r="D41" s="83"/>
+      <c r="J41" s="76" t="s">
+        <v>1703</v>
+      </c>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M41" s="76" t="s">
+        <v>307</v>
+      </c>
+      <c r="N41" s="84"/>
+    </row>
+    <row r="42" spans="4:14">
+      <c r="D42" s="83"/>
+      <c r="N42" s="84"/>
+    </row>
+    <row r="43" spans="4:14">
+      <c r="D43" s="83"/>
+      <c r="M43" s="88" t="s">
         <v>1712</v>
       </c>
-      <c r="N26" s="85"/>
-    </row>
-    <row r="27" spans="4:18">
-      <c r="D27" s="84"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="77" t="s">
-        <v>1297</v>
-      </c>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M27" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N27" s="85"/>
-    </row>
-    <row r="28" spans="4:18">
-      <c r="D28" s="84"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="77" t="s">
-        <v>1291</v>
-      </c>
-      <c r="K28" s="77"/>
-      <c r="L28" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M28" s="77" t="s">
-        <v>1708</v>
-      </c>
-      <c r="N28" s="85"/>
-    </row>
-    <row r="29" spans="4:18">
-      <c r="D29" s="84"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="77" t="s">
-        <v>1206</v>
-      </c>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M29" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N29" s="85"/>
-    </row>
-    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
-      <c r="D30" s="84"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="77" t="s">
-        <v>1203</v>
-      </c>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M30" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N30" s="85"/>
-    </row>
-    <row r="31" spans="4:18">
-      <c r="D31" s="84"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="77" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K31" s="77"/>
-      <c r="L31" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M31" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N31" s="85"/>
-    </row>
-    <row r="32" spans="4:18">
-      <c r="D32" s="84"/>
-      <c r="E32" s="65" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F32" s="65" t="s">
-        <v>1710</v>
-      </c>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="77" t="s">
-        <v>1196</v>
-      </c>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M32" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N32" s="85"/>
-    </row>
-    <row r="33" spans="4:14">
-      <c r="D33" s="84"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="77" t="s">
-        <v>1186</v>
-      </c>
-      <c r="K33" s="77"/>
-      <c r="L33" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M33" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N33" s="85"/>
-    </row>
-    <row r="34" spans="4:14">
-      <c r="D34" s="84"/>
-      <c r="E34" s="65" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="77" t="s">
-        <v>1211</v>
-      </c>
-      <c r="K34" s="77"/>
-      <c r="L34" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M34" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N34" s="85"/>
-    </row>
-    <row r="35" spans="4:14">
-      <c r="D35" s="84"/>
-      <c r="E35" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="77" t="s">
-        <v>1216</v>
-      </c>
-      <c r="K35" s="77"/>
-      <c r="L35" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M35" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N35" s="85"/>
-    </row>
-    <row r="36" spans="4:14">
-      <c r="D36" s="84"/>
-      <c r="E36" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="77" t="s">
-        <v>1217</v>
-      </c>
-      <c r="K36" s="77"/>
-      <c r="L36" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M36" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N36" s="85"/>
-    </row>
-    <row r="37" spans="4:14">
-      <c r="D37" s="84"/>
-      <c r="E37" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="77" t="s">
-        <v>1253</v>
-      </c>
-      <c r="K37" s="77"/>
-      <c r="L37" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M37" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N37" s="85"/>
-    </row>
-    <row r="38" spans="4:14">
-      <c r="D38" s="84"/>
-      <c r="E38" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="77" t="s">
-        <v>1195</v>
-      </c>
-      <c r="K38" s="77"/>
-      <c r="L38" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M38" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N38" s="85"/>
-    </row>
-    <row r="39" spans="4:14">
-      <c r="D39" s="84"/>
-      <c r="E39" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="77" t="s">
-        <v>1702</v>
-      </c>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M39" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N39" s="85"/>
-    </row>
-    <row r="40" spans="4:14">
-      <c r="D40" s="84"/>
-      <c r="E40" s="65" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="77" t="s">
-        <v>1703</v>
-      </c>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M40" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N40" s="85"/>
-    </row>
-    <row r="41" spans="4:14">
-      <c r="D41" s="84"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="77" t="s">
-        <v>1704</v>
-      </c>
-      <c r="K41" s="77"/>
-      <c r="L41" s="77" t="s">
-        <v>1707</v>
-      </c>
-      <c r="M41" s="77" t="s">
-        <v>307</v>
-      </c>
-      <c r="N41" s="85"/>
-    </row>
-    <row r="42" spans="4:14">
-      <c r="D42" s="84"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="65"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="65"/>
-      <c r="N42" s="85"/>
-    </row>
-    <row r="43" spans="4:14">
-      <c r="D43" s="84"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="89" t="s">
-        <v>1713</v>
-      </c>
-      <c r="N43" s="85"/>
+      <c r="N43" s="84"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="84"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="85"/>
+      <c r="D44" s="83"/>
+      <c r="N44" s="84"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="86"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="87"/>
-      <c r="H45" s="87"/>
-      <c r="I45" s="87"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="87"/>
-      <c r="N45" s="88"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="86"/>
+      <c r="F45" s="86"/>
+      <c r="G45" s="86"/>
+      <c r="H45" s="86"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="86"/>
+      <c r="L45" s="86"/>
+      <c r="M45" s="86"/>
+      <c r="N45" s="87"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -13005,7 +12806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:L160"/>
+  <dimension ref="B3:L159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -13026,7 +12827,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="6" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1153</v>
@@ -13234,7 +13035,7 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="6" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1154</v>
@@ -13550,7 +13351,7 @@
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="6" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1155</v>
@@ -13810,7 +13611,7 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="6" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>1156</v>
@@ -14088,7 +13889,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="6" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>1157</v>
@@ -14192,7 +13993,7 @@
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="6" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>1158</v>
@@ -15034,7 +14835,7 @@
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="6" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>1159</v>
@@ -15242,7 +15043,7 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="6" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>1160</v>
@@ -15340,7 +15141,7 @@
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="6" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>1396</v>
@@ -15435,7 +15236,7 @@
         <v>125</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K95" s="5" t="str">
         <f t="shared" si="11"/>
@@ -15447,7 +15248,7 @@
         <v>1395</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8">
@@ -15464,7 +15265,7 @@
         <v>1238</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="K96" s="5" t="str">
         <f t="shared" si="11"/>
@@ -15502,7 +15303,7 @@
         <v>1395</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8">
@@ -15516,7 +15317,7 @@
         <v>125</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="K98" s="5" t="str">
         <f t="shared" si="12"/>
@@ -15528,7 +15329,7 @@
         <v>1395</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8">
@@ -15542,7 +15343,7 @@
         <v>125</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="K99" s="5" t="str">
         <f t="shared" si="12"/>
@@ -15554,7 +15355,7 @@
         <v>1395</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8">
@@ -15568,7 +15369,7 @@
         <v>125</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K100" s="5" t="str">
         <f t="shared" ref="K100:K101" si="13">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B100&amp;"'"&amp;","&amp;E100&amp;","&amp;"'"&amp;C100&amp;"'"&amp;","&amp;"'"&amp;D100&amp;"'"&amp;","&amp;"'"&amp;F100&amp;"'"&amp;","&amp;G100&amp;","&amp;H100&amp;","&amp;"'"&amp;I100&amp;"'"&amp;");"</f>
@@ -15580,7 +15381,7 @@
         <v>1395</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8">
@@ -15594,7 +15395,7 @@
         <v>125</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K101" s="5" t="str">
         <f t="shared" si="13"/>
@@ -15606,7 +15407,7 @@
         <v>1395</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8">
@@ -15620,7 +15421,7 @@
         <v>125</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K102" s="5" t="str">
         <f t="shared" ref="K102:K104" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
@@ -15632,7 +15433,7 @@
         <v>1395</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8">
@@ -15646,7 +15447,7 @@
         <v>125</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K103" s="5" t="str">
         <f t="shared" si="14"/>
@@ -15658,7 +15459,7 @@
         <v>1395</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8">
@@ -15672,7 +15473,7 @@
         <v>125</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K104" s="5" t="str">
         <f t="shared" si="14"/>
@@ -15681,7 +15482,7 @@
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="6" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>1398</v>
@@ -16632,14 +16433,14 @@
         <v>1427</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
         <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -16648,7 +16449,7 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="15"/>
@@ -16660,14 +16461,14 @@
         <v>1427</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
         <v>34</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -16676,7 +16477,7 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" ref="K140" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
@@ -16688,14 +16489,14 @@
         <v>1427</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
         <v>35</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -16704,7 +16505,7 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
@@ -16716,14 +16517,14 @@
         <v>1427</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
         <v>36</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -16732,7 +16533,7 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K142" s="5" t="str">
         <f t="shared" si="15"/>
@@ -16740,67 +16541,67 @@
       </c>
     </row>
     <row r="143" spans="2:11">
-      <c r="B143" s="8" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8">
-        <v>99</v>
-      </c>
-      <c r="F143" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="G143" s="9">
-        <v>0</v>
-      </c>
-      <c r="H143" s="9" t="s">
+      <c r="B143" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11">
+      <c r="B144" s="8" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8">
+        <v>1</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G144" s="9">
+        <v>0</v>
+      </c>
+      <c r="H144" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I143" s="8"/>
-      <c r="K143" s="5" t="str">
-        <f t="shared" ref="K143:K160" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',99,'省略','','省略',0,0.0,'');</v>
-      </c>
-    </row>
-    <row r="144" spans="2:11">
-      <c r="B144" s="6" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>133</v>
+      <c r="I144" s="8"/>
+      <c r="K144" s="5" t="str">
+        <f t="shared" ref="K144:K159" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1516</v>
+        <v>1529</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>1533</v>
@@ -16814,19 +16615,19 @@
       <c r="I145" s="8"/>
       <c r="K145" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',1,'Red','','レッド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1530</v>
+        <v>1516</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>1534</v>
@@ -16840,19 +16641,19 @@
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',2,'Pink','','ピンク',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>1517</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>1535</v>
@@ -16866,19 +16667,19 @@
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>1518</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>1536</v>
@@ -16892,19 +16693,19 @@
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>1519</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>1537</v>
@@ -16918,19 +16719,19 @@
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>1520</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>1538</v>
@@ -16944,19 +16745,19 @@
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
       <c r="B151" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>1521</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>1539</v>
@@ -16970,19 +16771,19 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
       <c r="B152" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>1522</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>1540</v>
@@ -16996,19 +16797,19 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
       <c r="B153" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>1523</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>1541</v>
@@ -17022,19 +16823,19 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
       <c r="B154" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>1524</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>1542</v>
@@ -17048,19 +16849,19 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
       <c r="B155" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>1525</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>1543</v>
@@ -17074,19 +16875,19 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
       <c r="B156" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>1544</v>
@@ -17100,19 +16901,19 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
       <c r="B157" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>1545</v>
@@ -17126,19 +16927,19 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
       <c r="B158" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>1527</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>1546</v>
@@ -17152,19 +16953,19 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
       <c r="B159" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>1528</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>1547</v>
@@ -17177,32 +16978,6 @@
       </c>
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('code011',15,'Silver','','シルバー',0,0.0,'');</v>
-      </c>
-    </row>
-    <row r="160" spans="2:11">
-      <c r="B160" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>1529</v>
-      </c>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8">
-        <v>99</v>
-      </c>
-      <c r="F160" s="8" t="s">
-        <v>1548</v>
-      </c>
-      <c r="G160" s="9">
-        <v>0</v>
-      </c>
-      <c r="H160" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I160" s="8"/>
-      <c r="K160" s="5" t="str">
         <f t="shared" si="18"/>
         <v>INSERT INTO m_code VALUES ('code011',99,'Others','','その他',0,0.0,'');</v>
       </c>
@@ -40890,7 +40665,7 @@
         <v>1304</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18">
@@ -40901,7 +40676,7 @@
         <v>1288</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D4" s="60" t="s">
         <v>1238</v>
@@ -40919,7 +40694,7 @@
         <v>1305</v>
       </c>
       <c r="O4" s="62" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="13.2">
@@ -40988,7 +40763,7 @@
         <v>1389</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="13.2">
@@ -41017,7 +40792,7 @@
         <v>1390</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="13.2">
@@ -41043,7 +40818,7 @@
         <v>1206</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.2">

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A230908B-C406-4C74-BC0A-0233EEDC9353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>

--- a/設計メモ.xlsx
+++ b/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A230908B-C406-4C74-BC0A-0233EEDC9353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E1566A-D666-476A-8D67-45ABB84859F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -15511,14 +15511,14 @@
         <v>1427</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>1434</v>
+        <v>1450</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
@@ -15526,10 +15526,12 @@
       <c r="H106" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I106" s="8"/>
+      <c r="I106" s="8" t="s">
+        <v>1474</v>
+      </c>
       <c r="K106" s="5" t="str">
-        <f t="shared" ref="K106:K142" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',0,'Unknown','','？？',0,0.0,'');</v>
+        <f t="shared" ref="K106:K141" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="107" spans="2:11">
@@ -15537,14 +15539,14 @@
         <v>1427</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -15553,11 +15555,11 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="K107" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="108" spans="2:11">
@@ -15565,14 +15567,14 @@
         <v>1427</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -15581,11 +15583,11 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="K108" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -15593,14 +15595,14 @@
         <v>1427</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -15609,11 +15611,11 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="K109" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -15621,14 +15623,14 @@
         <v>1427</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -15637,11 +15639,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="K110" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -15649,14 +15651,14 @@
         <v>1427</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1440</v>
+        <v>1399</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -15665,11 +15667,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -15677,14 +15679,14 @@
         <v>1427</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1399</v>
+        <v>1441</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -15693,11 +15695,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -15705,14 +15707,14 @@
         <v>1427</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1441</v>
+        <v>1400</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1455</v>
+        <v>1418</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -15721,11 +15723,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -15733,14 +15735,14 @@
         <v>1427</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1400</v>
+        <v>1442</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1418</v>
+        <v>1456</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -15749,11 +15751,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -15761,14 +15763,14 @@
         <v>1427</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1442</v>
+        <v>1407</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -15777,11 +15779,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -15789,14 +15791,14 @@
         <v>1427</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1407</v>
+        <v>1443</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -15805,11 +15807,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -15817,14 +15819,14 @@
         <v>1427</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1443</v>
+        <v>1401</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1458</v>
+        <v>1419</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -15833,11 +15835,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -15845,14 +15847,14 @@
         <v>1427</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1419</v>
+        <v>1459</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -15861,11 +15863,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -15873,14 +15875,14 @@
         <v>1427</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -15889,11 +15891,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -15901,14 +15903,14 @@
         <v>1427</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1403</v>
+        <v>1412</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -15917,11 +15919,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -15929,14 +15931,14 @@
         <v>1427</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -15945,11 +15947,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -15957,14 +15959,14 @@
         <v>1427</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -15973,11 +15975,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -15985,14 +15987,14 @@
         <v>1427</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1409</v>
+        <v>1444</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -16001,11 +16003,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -16013,14 +16015,14 @@
         <v>1427</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -16029,11 +16031,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -16041,14 +16043,14 @@
         <v>1427</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1445</v>
+        <v>1404</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -16057,11 +16059,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -16069,14 +16071,14 @@
         <v>1427</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1404</v>
+        <v>1446</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1464</v>
+        <v>1420</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -16085,11 +16087,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -16097,14 +16099,14 @@
         <v>1427</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1446</v>
+        <v>1410</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -16113,11 +16115,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -16125,14 +16127,14 @@
         <v>1427</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1421</v>
+        <v>1467</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -16141,11 +16143,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -16153,14 +16155,14 @@
         <v>1427</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -16169,11 +16171,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1495</v>
+        <v>1426</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -16181,14 +16183,14 @@
         <v>1427</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1406</v>
+        <v>1447</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -16197,11 +16199,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1426</v>
+        <v>1496</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -16209,14 +16211,14 @@
         <v>1427</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1447</v>
+        <v>1411</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -16225,11 +16227,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -16237,14 +16239,14 @@
         <v>1427</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -16253,11 +16255,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -16265,14 +16267,14 @@
         <v>1427</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1471</v>
+        <v>1422</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -16281,11 +16283,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -16293,14 +16295,14 @@
         <v>1427</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -16309,11 +16311,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -16321,14 +16323,14 @@
         <v>1427</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -16337,11 +16339,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -16349,14 +16351,14 @@
         <v>1427</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -16365,11 +16367,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -16377,14 +16379,14 @@
         <v>1427</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1417</v>
+        <v>1448</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1425</v>
+        <v>1472</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -16393,11 +16395,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -16405,14 +16407,14 @@
         <v>1427</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1448</v>
+        <v>1570</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1472</v>
+        <v>1571</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -16421,11 +16423,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1503</v>
+        <v>1572</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('code010',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -16433,14 +16435,14 @@
         <v>1427</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -16449,11 +16451,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <f t="shared" ref="K139" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -16461,14 +16463,14 @@
         <v>1427</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -16477,11 +16479,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" ref="K140" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" ref="K140" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -16489,14 +16491,14 @@
         <v>1427</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -16505,11 +16507,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code010',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('code010',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -16517,14 +16519,14 @@
         <v>1427</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1578</v>
+        <v>1435</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1579</v>
+        <v>1434</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -16532,12 +16534,10 @@
       <c r="H142" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I142" s="8" t="s">
-        <v>1580</v>
-      </c>
+      <c r="I142" s="8"/>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('code010',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code010',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -20536,7 +20536,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -20632,7 +20632,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -20665,7 +20665,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -20695,7 +20695,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -20728,7 +20728,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -20758,7 +20758,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -20824,7 +20824,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -20887,7 +20887,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -20920,7 +20920,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -20950,7 +20950,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -20983,7 +20983,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -21046,7 +21046,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -21142,7 +21142,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -21205,7 +21205,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -21238,7 +21238,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -21268,7 +21268,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -21331,7 +21331,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -21364,7 +21364,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -21397,7 +21397,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -21430,7 +21430,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -21460,7 +21460,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -21493,7 +21493,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -21526,7 +21526,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -21556,7 +21556,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -21589,7 +21589,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -21653,7 +21653,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -21686,7 +21686,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -21815,7 +21815,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -21848,7 +21848,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -21878,7 +21878,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -21911,7 +21911,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -21944,7 +21944,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -21974,7 +21974,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -22070,7 +22070,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -22100,7 +22100,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -22190,7 +22190,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -22256,7 +22256,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -22286,7 +22286,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -22316,7 +22316,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -22346,7 +22346,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -22379,7 +22379,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -22412,7 +22412,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -22475,7 +22475,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -22508,7 +22508,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -22541,7 +22541,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -22571,7 +22571,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -22601,7 +22601,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -22661,7 +22661,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -22751,7 +22751,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -22781,7 +22781,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -22811,7 +22811,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -22871,7 +22871,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -22901,7 +22901,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -22931,7 +22931,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -22963,7 +22963,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -22995,7 +22995,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -23025,7 +23025,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -23058,7 +23058,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -23091,7 +23091,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -23121,7 +23121,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>
